--- a/public/results/2025/2025 Weekly Stats - Week 16.xlsx
+++ b/public/results/2025/2025 Weekly Stats - Week 16.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mthutter/CODE/golf-league-site/public/results/2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F3E9679-B22E-BE48-B90E-026CADEA75C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{204337AF-8863-DD46-AF0E-BF0A4C2C9D09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1300" yWindow="500" windowWidth="28100" windowHeight="19840" firstSheet="3" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -450,9 +450,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -597,14 +594,17 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1063,7 +1063,7 @@
   <dimension ref="A1:Z21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="23" style="29" customWidth="1"/>
+    <col min="1" max="1" width="23" style="28" customWidth="1"/>
     <col min="2" max="2" width="15" style="2" customWidth="1"/>
     <col min="3" max="11" width="5" style="2" customWidth="1"/>
     <col min="12" max="12" width="5.1640625" style="2" bestFit="1" customWidth="1"/>
@@ -1074,34 +1074,34 @@
     <col min="17" max="17" width="15.1640625" style="2" customWidth="1"/>
     <col min="18" max="18" width="13.6640625" style="2" customWidth="1"/>
     <col min="19" max="19" width="8.6640625" style="2" customWidth="1"/>
-    <col min="20" max="20" width="8.6640625" style="32" customWidth="1"/>
+    <col min="20" max="20" width="8.6640625" style="31" customWidth="1"/>
     <col min="21" max="26" width="8.6640625" style="2" customWidth="1"/>
     <col min="27" max="16384" width="14.1640625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
+      <c r="A1" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
-      <c r="T1" s="30"/>
+      <c r="T1" s="29"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
@@ -1110,28 +1110,28 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A2" s="57" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
+      <c r="A2" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
-      <c r="T2" s="30"/>
+      <c r="T2" s="29"/>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
@@ -1155,11 +1155,11 @@
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
       <c r="O3" s="5"/>
-      <c r="P3" s="61"/>
-      <c r="Q3" s="61"/>
+      <c r="P3" s="60"/>
+      <c r="Q3" s="60"/>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
-      <c r="T3" s="30"/>
+      <c r="T3" s="29"/>
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
       <c r="W3" s="1"/>
@@ -1168,56 +1168,56 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.25">
-      <c r="A4" s="65" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="20">
-        <v>1</v>
-      </c>
-      <c r="D4" s="20">
-        <v>2</v>
-      </c>
-      <c r="E4" s="20">
-        <v>3</v>
-      </c>
-      <c r="F4" s="20">
-        <v>4</v>
-      </c>
-      <c r="G4" s="20">
-        <v>5</v>
-      </c>
-      <c r="H4" s="20">
-        <v>6</v>
-      </c>
-      <c r="I4" s="20">
+      <c r="A4" s="64" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="19">
+        <v>1</v>
+      </c>
+      <c r="D4" s="19">
+        <v>2</v>
+      </c>
+      <c r="E4" s="19">
+        <v>3</v>
+      </c>
+      <c r="F4" s="19">
+        <v>4</v>
+      </c>
+      <c r="G4" s="19">
+        <v>5</v>
+      </c>
+      <c r="H4" s="19">
+        <v>6</v>
+      </c>
+      <c r="I4" s="19">
         <v>7</v>
       </c>
-      <c r="J4" s="20">
+      <c r="J4" s="19">
         <v>8</v>
       </c>
-      <c r="K4" s="20">
+      <c r="K4" s="19">
         <v>9</v>
       </c>
-      <c r="L4" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="M4" s="20" t="s">
+      <c r="L4" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="M4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="N4" s="20" t="s">
+      <c r="N4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="O4" s="21" t="s">
+      <c r="O4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="P4" s="62"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="28"/>
+      <c r="P4" s="61"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="27"/>
       <c r="S4" s="3"/>
-      <c r="T4" s="31"/>
+      <c r="T4" s="30"/>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
@@ -1226,7 +1226,7 @@
       <c r="Z4" s="3"/>
     </row>
     <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A5" s="66"/>
+      <c r="A5" s="65"/>
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="62"/>
-      <c r="Q5" s="64"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="61"/>
+      <c r="Q5" s="63"/>
       <c r="R5" s="4"/>
       <c r="S5" s="3"/>
-      <c r="T5" s="31"/>
+      <c r="T5" s="30"/>
       <c r="U5" s="3"/>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
@@ -1277,46 +1277,46 @@
       <c r="Z5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="67"/>
-      <c r="B6" s="25" t="s">
+      <c r="A6" s="66"/>
+      <c r="B6" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="25">
-        <v>4</v>
-      </c>
-      <c r="D6" s="25">
-        <v>1</v>
-      </c>
-      <c r="E6" s="25">
-        <v>3</v>
-      </c>
-      <c r="F6" s="25">
+      <c r="C6" s="24">
+        <v>4</v>
+      </c>
+      <c r="D6" s="24">
+        <v>1</v>
+      </c>
+      <c r="E6" s="24">
+        <v>3</v>
+      </c>
+      <c r="F6" s="24">
         <v>9</v>
       </c>
-      <c r="G6" s="25">
-        <v>5</v>
-      </c>
-      <c r="H6" s="25">
+      <c r="G6" s="24">
+        <v>5</v>
+      </c>
+      <c r="H6" s="24">
         <v>7</v>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="24">
         <v>8</v>
       </c>
-      <c r="J6" s="25">
-        <v>6</v>
-      </c>
-      <c r="K6" s="25">
-        <v>2</v>
-      </c>
-      <c r="L6" s="26"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="27"/>
+      <c r="J6" s="24">
+        <v>6</v>
+      </c>
+      <c r="K6" s="24">
+        <v>2</v>
+      </c>
+      <c r="L6" s="25"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="26"/>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
-      <c r="T6" s="31"/>
+      <c r="T6" s="30"/>
       <c r="U6" s="3"/>
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
@@ -1325,7 +1325,7 @@
       <c r="Z6" s="3"/>
     </row>
     <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A7" s="68"/>
+      <c r="A7" s="67"/>
       <c r="B7" s="12" t="s">
         <v>23</v>
       </c>
@@ -1352,7 +1352,7 @@
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
-      <c r="T7" s="30"/>
+      <c r="T7" s="29"/>
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
       <c r="W7" s="1"/>
@@ -1361,7 +1361,7 @@
       <c r="Z7" s="1"/>
     </row>
     <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="69"/>
+      <c r="A8" s="68"/>
       <c r="B8" s="16" t="s">
         <v>25</v>
       </c>
@@ -1412,18 +1412,18 @@
         <v/>
       </c>
       <c r="P8" s="1"/>
-      <c r="Q8" s="33"/>
-      <c r="R8" s="30"/>
+      <c r="Q8" s="32"/>
+      <c r="R8" s="29"/>
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
       <c r="W8" s="1"/>
       <c r="X8" s="1"/>
-      <c r="Z8" s="34"/>
+      <c r="Z8" s="33"/>
     </row>
     <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A9" s="68"/>
+      <c r="A9" s="67"/>
       <c r="B9" s="12"/>
       <c r="C9" s="12"/>
       <c r="D9" s="12"/>
@@ -1446,11 +1446,11 @@
       <c r="O9" s="14"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
-      <c r="R9" s="30"/>
+      <c r="R9" s="29"/>
       <c r="T9" s="2"/>
     </row>
     <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="69"/>
+      <c r="A10" s="68"/>
       <c r="B10" s="16"/>
       <c r="C10" s="16" t="str">
         <f>IF(C9&gt;0, VLOOKUP(C9-C$5-(INT($M9/9)+(MOD($M9,9)&gt;=C$6)), 'Point System'!$A$4:$B$15, 2),"")</f>
@@ -1500,11 +1500,11 @@
       </c>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
-      <c r="R10" s="30"/>
+      <c r="R10" s="29"/>
       <c r="T10" s="2"/>
     </row>
     <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A11" s="68"/>
+      <c r="A11" s="67"/>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -1527,12 +1527,12 @@
       <c r="O11" s="14"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
-      <c r="R11" s="30"/>
+      <c r="R11" s="29"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
     <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="69"/>
+      <c r="A12" s="68"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16" t="str">
         <f>IF(C11&gt;0, VLOOKUP(C11-C$5-(INT($M11/9)+(MOD($M11,9)&gt;=C$6)), 'Point System'!$A$4:$B$15, 2),"")</f>
@@ -1580,14 +1580,14 @@
         <f>IF(L12&lt;&gt;"", L12, "")</f>
         <v/>
       </c>
-      <c r="P12" s="33"/>
-      <c r="Q12" s="33"/>
-      <c r="R12" s="30"/>
+      <c r="P12" s="32"/>
+      <c r="Q12" s="32"/>
+      <c r="R12" s="29"/>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
     </row>
     <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A13" s="68"/>
+      <c r="A13" s="67"/>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
@@ -1609,13 +1609,13 @@
       </c>
       <c r="O13" s="14"/>
       <c r="P13" s="1"/>
-      <c r="Q13" s="33"/>
-      <c r="R13" s="30"/>
+      <c r="Q13" s="32"/>
+      <c r="R13" s="29"/>
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
     </row>
     <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="69"/>
+      <c r="A14" s="68"/>
       <c r="B14" s="16"/>
       <c r="C14" s="16" t="str">
         <f>IF(C13&gt;0, VLOOKUP(C13-C$5-(INT($M13/9)+(MOD($M13,9)&gt;=C$6)), 'Point System'!$A$4:$B$15, 2),"")</f>
@@ -1663,14 +1663,14 @@
         <f>IF(L14&lt;&gt;"", L14, "")</f>
         <v/>
       </c>
-      <c r="P14" s="33"/>
-      <c r="Q14" s="33"/>
-      <c r="R14" s="30"/>
+      <c r="P14" s="32"/>
+      <c r="Q14" s="32"/>
+      <c r="R14" s="29"/>
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
     </row>
     <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A15" s="68"/>
+      <c r="A15" s="67"/>
       <c r="B15" s="12"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
@@ -1692,8 +1692,8 @@
       </c>
       <c r="O15" s="14"/>
       <c r="P15" s="1"/>
-      <c r="Q15" s="33"/>
-      <c r="R15" s="30"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="29"/>
       <c r="V15" s="1"/>
       <c r="W15" s="1"/>
       <c r="X15" s="1"/>
@@ -1701,7 +1701,7 @@
       <c r="Z15" s="1"/>
     </row>
     <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="69"/>
+      <c r="A16" s="68"/>
       <c r="B16" s="16"/>
       <c r="C16" s="16" t="str">
         <f>IF(C15&gt;0, VLOOKUP(C15-C$5-(INT($M15/9)+(MOD($M15,9)&gt;=C$6)), 'Point System'!$A$4:$B$15, 2),"")</f>
@@ -1749,9 +1749,9 @@
         <f>IF(L16&lt;&gt;"", L16, "")</f>
         <v/>
       </c>
-      <c r="P16" s="33"/>
-      <c r="Q16" s="33"/>
-      <c r="R16" s="30"/>
+      <c r="P16" s="32"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="29"/>
       <c r="V16" s="1"/>
       <c r="W16" s="1"/>
       <c r="X16" s="1"/>
@@ -1759,7 +1759,7 @@
       <c r="Z16" s="1"/>
     </row>
     <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A17" s="68"/>
+      <c r="A17" s="67"/>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -1781,8 +1781,8 @@
       </c>
       <c r="O17" s="14"/>
       <c r="P17" s="1"/>
-      <c r="Q17" s="33"/>
-      <c r="R17" s="30"/>
+      <c r="Q17" s="32"/>
+      <c r="R17" s="29"/>
       <c r="V17" s="1"/>
       <c r="W17" s="1"/>
       <c r="X17" s="1"/>
@@ -1790,7 +1790,7 @@
       <c r="Z17" s="1"/>
     </row>
     <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="69"/>
+      <c r="A18" s="68"/>
       <c r="B18" s="16"/>
       <c r="C18" s="16" t="str">
         <f>IF(C17&gt;0, VLOOKUP(C17-C$5-(INT($M17/9)+(MOD($M17,9)&gt;=C$6)), 'Point System'!$A$4:$B$15, 2),"")</f>
@@ -1838,9 +1838,9 @@
         <f>IF(L18&lt;&gt;"", L18, "")</f>
         <v/>
       </c>
-      <c r="P18" s="33"/>
-      <c r="Q18" s="33"/>
-      <c r="R18" s="30"/>
+      <c r="P18" s="32"/>
+      <c r="Q18" s="32"/>
+      <c r="R18" s="29"/>
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
       <c r="X18" s="1"/>
@@ -1848,7 +1848,7 @@
       <c r="Z18" s="1"/>
     </row>
     <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A19" s="68"/>
+      <c r="A19" s="67"/>
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -1871,11 +1871,11 @@
       <c r="O19" s="14"/>
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
-      <c r="R19" s="30"/>
+      <c r="R19" s="29"/>
       <c r="T19" s="2"/>
     </row>
     <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="69"/>
+      <c r="A20" s="68"/>
       <c r="B20" s="16"/>
       <c r="C20" s="16" t="str">
         <f>IF(C19&gt;0, VLOOKUP(C19-C$5-(INT($M19/9)+(MOD($M19,9)&gt;=C$6)), 'Point System'!$A$4:$B$15, 2),"")</f>
@@ -1925,15 +1925,15 @@
       </c>
       <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
-      <c r="R20" s="30"/>
+      <c r="R20" s="29"/>
       <c r="T20" s="2"/>
     </row>
     <row r="21" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E21" s="29"/>
-      <c r="G21" s="29"/>
-      <c r="H21" s="29"/>
-      <c r="J21" s="29"/>
-      <c r="K21" s="29"/>
+      <c r="E21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="J21" s="28"/>
+      <c r="K21" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1968,23 +1968,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
+      <c r="A1" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -1998,23 +1998,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="57" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
+      <c r="A2" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -2056,49 +2056,49 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="20">
-        <v>1</v>
-      </c>
-      <c r="D4" s="20">
-        <v>2</v>
-      </c>
-      <c r="E4" s="20">
-        <v>3</v>
-      </c>
-      <c r="F4" s="20">
-        <v>4</v>
-      </c>
-      <c r="G4" s="20">
-        <v>5</v>
-      </c>
-      <c r="H4" s="20">
-        <v>6</v>
-      </c>
-      <c r="I4" s="20">
+      <c r="A4" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="19">
+        <v>1</v>
+      </c>
+      <c r="D4" s="19">
+        <v>2</v>
+      </c>
+      <c r="E4" s="19">
+        <v>3</v>
+      </c>
+      <c r="F4" s="19">
+        <v>4</v>
+      </c>
+      <c r="G4" s="19">
+        <v>5</v>
+      </c>
+      <c r="H4" s="19">
+        <v>6</v>
+      </c>
+      <c r="I4" s="19">
         <v>7</v>
       </c>
-      <c r="J4" s="20">
+      <c r="J4" s="19">
         <v>8</v>
       </c>
-      <c r="K4" s="20">
+      <c r="K4" s="19">
         <v>9</v>
       </c>
-      <c r="L4" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="M4" s="20" t="s">
+      <c r="L4" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="M4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="N4" s="20" t="s">
+      <c r="N4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="O4" s="21" t="s">
+      <c r="O4" s="20" t="s">
         <v>9</v>
       </c>
       <c r="P4" s="3"/>
@@ -2114,7 +2114,7 @@
       <c r="Z4" s="3"/>
     </row>
     <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A5" s="22"/>
+      <c r="A5" s="21"/>
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
-      <c r="O5" s="23"/>
+      <c r="O5" s="22"/>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
@@ -2165,41 +2165,41 @@
       <c r="Z5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24"/>
-      <c r="B6" s="25" t="s">
+      <c r="A6" s="23"/>
+      <c r="B6" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="25">
-        <v>4</v>
-      </c>
-      <c r="D6" s="25">
-        <v>1</v>
-      </c>
-      <c r="E6" s="25">
-        <v>3</v>
-      </c>
-      <c r="F6" s="25">
+      <c r="C6" s="24">
+        <v>4</v>
+      </c>
+      <c r="D6" s="24">
+        <v>1</v>
+      </c>
+      <c r="E6" s="24">
+        <v>3</v>
+      </c>
+      <c r="F6" s="24">
         <v>9</v>
       </c>
-      <c r="G6" s="25">
-        <v>5</v>
-      </c>
-      <c r="H6" s="25">
+      <c r="G6" s="24">
+        <v>5</v>
+      </c>
+      <c r="H6" s="24">
         <v>7</v>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="24">
         <v>8</v>
       </c>
-      <c r="J6" s="25">
-        <v>6</v>
-      </c>
-      <c r="K6" s="25">
-        <v>2</v>
-      </c>
-      <c r="L6" s="26"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="27"/>
+      <c r="J6" s="24">
+        <v>6</v>
+      </c>
+      <c r="K6" s="24">
+        <v>2</v>
+      </c>
+      <c r="L6" s="25"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="26"/>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
@@ -3536,23 +3536,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
+      <c r="A1" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -3566,23 +3566,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="57" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
+      <c r="A2" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -3624,49 +3624,49 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="20">
-        <v>1</v>
-      </c>
-      <c r="D4" s="20">
-        <v>2</v>
-      </c>
-      <c r="E4" s="20">
-        <v>3</v>
-      </c>
-      <c r="F4" s="20">
-        <v>4</v>
-      </c>
-      <c r="G4" s="20">
-        <v>5</v>
-      </c>
-      <c r="H4" s="20">
-        <v>6</v>
-      </c>
-      <c r="I4" s="20">
+      <c r="A4" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="19">
+        <v>1</v>
+      </c>
+      <c r="D4" s="19">
+        <v>2</v>
+      </c>
+      <c r="E4" s="19">
+        <v>3</v>
+      </c>
+      <c r="F4" s="19">
+        <v>4</v>
+      </c>
+      <c r="G4" s="19">
+        <v>5</v>
+      </c>
+      <c r="H4" s="19">
+        <v>6</v>
+      </c>
+      <c r="I4" s="19">
         <v>7</v>
       </c>
-      <c r="J4" s="20">
+      <c r="J4" s="19">
         <v>8</v>
       </c>
-      <c r="K4" s="20">
+      <c r="K4" s="19">
         <v>9</v>
       </c>
-      <c r="L4" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="M4" s="20" t="s">
+      <c r="L4" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="M4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="N4" s="20" t="s">
+      <c r="N4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="O4" s="21" t="s">
+      <c r="O4" s="20" t="s">
         <v>9</v>
       </c>
       <c r="P4" s="3"/>
@@ -3682,7 +3682,7 @@
       <c r="Z4" s="3"/>
     </row>
     <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A5" s="22"/>
+      <c r="A5" s="21"/>
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
-      <c r="O5" s="23"/>
+      <c r="O5" s="22"/>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
@@ -3733,41 +3733,41 @@
       <c r="Z5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24"/>
-      <c r="B6" s="25" t="s">
+      <c r="A6" s="23"/>
+      <c r="B6" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="25">
-        <v>4</v>
-      </c>
-      <c r="D6" s="25">
-        <v>1</v>
-      </c>
-      <c r="E6" s="25">
-        <v>3</v>
-      </c>
-      <c r="F6" s="25">
+      <c r="C6" s="24">
+        <v>4</v>
+      </c>
+      <c r="D6" s="24">
+        <v>1</v>
+      </c>
+      <c r="E6" s="24">
+        <v>3</v>
+      </c>
+      <c r="F6" s="24">
         <v>9</v>
       </c>
-      <c r="G6" s="25">
-        <v>5</v>
-      </c>
-      <c r="H6" s="25">
+      <c r="G6" s="24">
+        <v>5</v>
+      </c>
+      <c r="H6" s="24">
         <v>7</v>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="24">
         <v>8</v>
       </c>
-      <c r="J6" s="25">
-        <v>6</v>
-      </c>
-      <c r="K6" s="25">
-        <v>2</v>
-      </c>
-      <c r="L6" s="26"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="27"/>
+      <c r="J6" s="24">
+        <v>6</v>
+      </c>
+      <c r="K6" s="24">
+        <v>2</v>
+      </c>
+      <c r="L6" s="25"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="26"/>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
@@ -4867,23 +4867,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
+      <c r="A1" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -4897,23 +4897,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="57" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
+      <c r="A2" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -4955,49 +4955,49 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="20">
-        <v>1</v>
-      </c>
-      <c r="D4" s="20">
-        <v>2</v>
-      </c>
-      <c r="E4" s="20">
-        <v>3</v>
-      </c>
-      <c r="F4" s="20">
-        <v>4</v>
-      </c>
-      <c r="G4" s="20">
-        <v>5</v>
-      </c>
-      <c r="H4" s="20">
-        <v>6</v>
-      </c>
-      <c r="I4" s="20">
+      <c r="A4" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="19">
+        <v>1</v>
+      </c>
+      <c r="D4" s="19">
+        <v>2</v>
+      </c>
+      <c r="E4" s="19">
+        <v>3</v>
+      </c>
+      <c r="F4" s="19">
+        <v>4</v>
+      </c>
+      <c r="G4" s="19">
+        <v>5</v>
+      </c>
+      <c r="H4" s="19">
+        <v>6</v>
+      </c>
+      <c r="I4" s="19">
         <v>7</v>
       </c>
-      <c r="J4" s="20">
+      <c r="J4" s="19">
         <v>8</v>
       </c>
-      <c r="K4" s="20">
+      <c r="K4" s="19">
         <v>9</v>
       </c>
-      <c r="L4" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="M4" s="20" t="s">
+      <c r="L4" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="M4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="N4" s="20" t="s">
+      <c r="N4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="O4" s="21" t="s">
+      <c r="O4" s="20" t="s">
         <v>9</v>
       </c>
       <c r="P4" s="3"/>
@@ -5013,7 +5013,7 @@
       <c r="Z4" s="3"/>
     </row>
     <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A5" s="22"/>
+      <c r="A5" s="21"/>
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -5050,7 +5050,7 @@
       </c>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
-      <c r="O5" s="23"/>
+      <c r="O5" s="22"/>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
@@ -5064,41 +5064,41 @@
       <c r="Z5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24"/>
-      <c r="B6" s="25" t="s">
+      <c r="A6" s="23"/>
+      <c r="B6" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="25">
-        <v>4</v>
-      </c>
-      <c r="D6" s="25">
-        <v>1</v>
-      </c>
-      <c r="E6" s="25">
-        <v>3</v>
-      </c>
-      <c r="F6" s="25">
+      <c r="C6" s="24">
+        <v>4</v>
+      </c>
+      <c r="D6" s="24">
+        <v>1</v>
+      </c>
+      <c r="E6" s="24">
+        <v>3</v>
+      </c>
+      <c r="F6" s="24">
         <v>9</v>
       </c>
-      <c r="G6" s="25">
-        <v>5</v>
-      </c>
-      <c r="H6" s="25">
+      <c r="G6" s="24">
+        <v>5</v>
+      </c>
+      <c r="H6" s="24">
         <v>7</v>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="24">
         <v>8</v>
       </c>
-      <c r="J6" s="25">
-        <v>6</v>
-      </c>
-      <c r="K6" s="25">
-        <v>2</v>
-      </c>
-      <c r="L6" s="26"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="27"/>
+      <c r="J6" s="24">
+        <v>6</v>
+      </c>
+      <c r="K6" s="24">
+        <v>2</v>
+      </c>
+      <c r="L6" s="25"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="26"/>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
@@ -6318,23 +6318,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
+      <c r="A1" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -6348,23 +6348,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="57" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
+      <c r="A2" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -6406,49 +6406,49 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="20">
-        <v>1</v>
-      </c>
-      <c r="D4" s="20">
-        <v>2</v>
-      </c>
-      <c r="E4" s="20">
-        <v>3</v>
-      </c>
-      <c r="F4" s="20">
-        <v>4</v>
-      </c>
-      <c r="G4" s="20">
-        <v>5</v>
-      </c>
-      <c r="H4" s="20">
-        <v>6</v>
-      </c>
-      <c r="I4" s="20">
+      <c r="A4" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="19">
+        <v>1</v>
+      </c>
+      <c r="D4" s="19">
+        <v>2</v>
+      </c>
+      <c r="E4" s="19">
+        <v>3</v>
+      </c>
+      <c r="F4" s="19">
+        <v>4</v>
+      </c>
+      <c r="G4" s="19">
+        <v>5</v>
+      </c>
+      <c r="H4" s="19">
+        <v>6</v>
+      </c>
+      <c r="I4" s="19">
         <v>7</v>
       </c>
-      <c r="J4" s="20">
+      <c r="J4" s="19">
         <v>8</v>
       </c>
-      <c r="K4" s="20">
+      <c r="K4" s="19">
         <v>9</v>
       </c>
-      <c r="L4" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="M4" s="20" t="s">
+      <c r="L4" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="M4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="N4" s="20" t="s">
+      <c r="N4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="O4" s="21" t="s">
+      <c r="O4" s="20" t="s">
         <v>9</v>
       </c>
       <c r="P4" s="3"/>
@@ -6464,7 +6464,7 @@
       <c r="Z4" s="3"/>
     </row>
     <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A5" s="22"/>
+      <c r="A5" s="21"/>
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -6501,7 +6501,7 @@
       </c>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
-      <c r="O5" s="23"/>
+      <c r="O5" s="22"/>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
@@ -6515,41 +6515,41 @@
       <c r="Z5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24"/>
-      <c r="B6" s="25" t="s">
+      <c r="A6" s="23"/>
+      <c r="B6" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="25">
-        <v>4</v>
-      </c>
-      <c r="D6" s="25">
-        <v>1</v>
-      </c>
-      <c r="E6" s="25">
-        <v>3</v>
-      </c>
-      <c r="F6" s="25">
+      <c r="C6" s="24">
+        <v>4</v>
+      </c>
+      <c r="D6" s="24">
+        <v>1</v>
+      </c>
+      <c r="E6" s="24">
+        <v>3</v>
+      </c>
+      <c r="F6" s="24">
         <v>9</v>
       </c>
-      <c r="G6" s="25">
-        <v>5</v>
-      </c>
-      <c r="H6" s="25">
+      <c r="G6" s="24">
+        <v>5</v>
+      </c>
+      <c r="H6" s="24">
         <v>7</v>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="24">
         <v>8</v>
       </c>
-      <c r="J6" s="25">
-        <v>6</v>
-      </c>
-      <c r="K6" s="25">
-        <v>2</v>
-      </c>
-      <c r="L6" s="26"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="27"/>
+      <c r="J6" s="24">
+        <v>6</v>
+      </c>
+      <c r="K6" s="24">
+        <v>2</v>
+      </c>
+      <c r="L6" s="25"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="26"/>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
@@ -6712,7 +6712,7 @@
       <c r="J9" s="12">
         <v>6</v>
       </c>
-      <c r="K9" s="54">
+      <c r="K9" s="53">
         <v>4</v>
       </c>
       <c r="L9" s="13">
@@ -7048,13 +7048,13 @@
       <c r="E15" s="12">
         <v>4</v>
       </c>
-      <c r="F15" s="54">
+      <c r="F15" s="53">
         <v>2</v>
       </c>
       <c r="G15" s="12">
         <v>5</v>
       </c>
-      <c r="H15" s="54">
+      <c r="H15" s="53">
         <v>3</v>
       </c>
       <c r="I15" s="12">
@@ -7165,7 +7165,7 @@
       <c r="E17" s="12">
         <v>4</v>
       </c>
-      <c r="F17" s="54">
+      <c r="F17" s="53">
         <v>2</v>
       </c>
       <c r="G17" s="12">
@@ -7861,7 +7861,7 @@
       <c r="C29" s="12">
         <v>6</v>
       </c>
-      <c r="D29" s="54">
+      <c r="D29" s="53">
         <v>4</v>
       </c>
       <c r="E29" s="12">
@@ -8120,23 +8120,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
+      <c r="A1" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -8150,23 +8150,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="57" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
+      <c r="A2" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -8208,49 +8208,49 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="20">
-        <v>1</v>
-      </c>
-      <c r="D4" s="20">
-        <v>2</v>
-      </c>
-      <c r="E4" s="20">
-        <v>3</v>
-      </c>
-      <c r="F4" s="20">
-        <v>4</v>
-      </c>
-      <c r="G4" s="20">
-        <v>5</v>
-      </c>
-      <c r="H4" s="20">
-        <v>6</v>
-      </c>
-      <c r="I4" s="20">
+      <c r="A4" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="19">
+        <v>1</v>
+      </c>
+      <c r="D4" s="19">
+        <v>2</v>
+      </c>
+      <c r="E4" s="19">
+        <v>3</v>
+      </c>
+      <c r="F4" s="19">
+        <v>4</v>
+      </c>
+      <c r="G4" s="19">
+        <v>5</v>
+      </c>
+      <c r="H4" s="19">
+        <v>6</v>
+      </c>
+      <c r="I4" s="19">
         <v>7</v>
       </c>
-      <c r="J4" s="20">
+      <c r="J4" s="19">
         <v>8</v>
       </c>
-      <c r="K4" s="20">
+      <c r="K4" s="19">
         <v>9</v>
       </c>
-      <c r="L4" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="M4" s="20" t="s">
+      <c r="L4" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="M4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="N4" s="20" t="s">
+      <c r="N4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="O4" s="21" t="s">
+      <c r="O4" s="20" t="s">
         <v>9</v>
       </c>
       <c r="P4" s="3"/>
@@ -8266,7 +8266,7 @@
       <c r="Z4" s="3"/>
     </row>
     <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A5" s="22"/>
+      <c r="A5" s="21"/>
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
-      <c r="O5" s="23"/>
+      <c r="O5" s="22"/>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
@@ -8317,41 +8317,41 @@
       <c r="Z5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24"/>
-      <c r="B6" s="25" t="s">
+      <c r="A6" s="23"/>
+      <c r="B6" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="25">
-        <v>4</v>
-      </c>
-      <c r="D6" s="25">
-        <v>1</v>
-      </c>
-      <c r="E6" s="25">
-        <v>3</v>
-      </c>
-      <c r="F6" s="25">
+      <c r="C6" s="24">
+        <v>4</v>
+      </c>
+      <c r="D6" s="24">
+        <v>1</v>
+      </c>
+      <c r="E6" s="24">
+        <v>3</v>
+      </c>
+      <c r="F6" s="24">
         <v>9</v>
       </c>
-      <c r="G6" s="25">
-        <v>5</v>
-      </c>
-      <c r="H6" s="25">
+      <c r="G6" s="24">
+        <v>5</v>
+      </c>
+      <c r="H6" s="24">
         <v>7</v>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="24">
         <v>8</v>
       </c>
-      <c r="J6" s="25">
-        <v>6</v>
-      </c>
-      <c r="K6" s="25">
-        <v>2</v>
-      </c>
-      <c r="L6" s="26"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="27"/>
+      <c r="J6" s="24">
+        <v>6</v>
+      </c>
+      <c r="K6" s="24">
+        <v>2</v>
+      </c>
+      <c r="L6" s="25"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="26"/>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
@@ -9922,23 +9922,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
+      <c r="A1" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -9952,23 +9952,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="57" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
+      <c r="A2" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -10010,49 +10010,49 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="20">
-        <v>1</v>
-      </c>
-      <c r="D4" s="20">
-        <v>2</v>
-      </c>
-      <c r="E4" s="20">
-        <v>3</v>
-      </c>
-      <c r="F4" s="20">
-        <v>4</v>
-      </c>
-      <c r="G4" s="20">
-        <v>5</v>
-      </c>
-      <c r="H4" s="20">
-        <v>6</v>
-      </c>
-      <c r="I4" s="20">
+      <c r="A4" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="19">
+        <v>1</v>
+      </c>
+      <c r="D4" s="19">
+        <v>2</v>
+      </c>
+      <c r="E4" s="19">
+        <v>3</v>
+      </c>
+      <c r="F4" s="19">
+        <v>4</v>
+      </c>
+      <c r="G4" s="19">
+        <v>5</v>
+      </c>
+      <c r="H4" s="19">
+        <v>6</v>
+      </c>
+      <c r="I4" s="19">
         <v>7</v>
       </c>
-      <c r="J4" s="20">
+      <c r="J4" s="19">
         <v>8</v>
       </c>
-      <c r="K4" s="20">
+      <c r="K4" s="19">
         <v>9</v>
       </c>
-      <c r="L4" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="M4" s="20" t="s">
+      <c r="L4" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="M4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="N4" s="20" t="s">
+      <c r="N4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="O4" s="21" t="s">
+      <c r="O4" s="20" t="s">
         <v>9</v>
       </c>
       <c r="P4" s="3"/>
@@ -10068,7 +10068,7 @@
       <c r="Z4" s="3"/>
     </row>
     <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A5" s="22"/>
+      <c r="A5" s="21"/>
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -10105,7 +10105,7 @@
       </c>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
-      <c r="O5" s="23"/>
+      <c r="O5" s="22"/>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
@@ -10119,41 +10119,41 @@
       <c r="Z5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24"/>
-      <c r="B6" s="25" t="s">
+      <c r="A6" s="23"/>
+      <c r="B6" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="25">
-        <v>4</v>
-      </c>
-      <c r="D6" s="25">
-        <v>1</v>
-      </c>
-      <c r="E6" s="25">
-        <v>3</v>
-      </c>
-      <c r="F6" s="25">
+      <c r="C6" s="24">
+        <v>4</v>
+      </c>
+      <c r="D6" s="24">
+        <v>1</v>
+      </c>
+      <c r="E6" s="24">
+        <v>3</v>
+      </c>
+      <c r="F6" s="24">
         <v>9</v>
       </c>
-      <c r="G6" s="25">
-        <v>5</v>
-      </c>
-      <c r="H6" s="25">
+      <c r="G6" s="24">
+        <v>5</v>
+      </c>
+      <c r="H6" s="24">
         <v>7</v>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="24">
         <v>8</v>
       </c>
-      <c r="J6" s="25">
-        <v>6</v>
-      </c>
-      <c r="K6" s="25">
-        <v>2</v>
-      </c>
-      <c r="L6" s="26"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="27"/>
+      <c r="J6" s="24">
+        <v>6</v>
+      </c>
+      <c r="K6" s="24">
+        <v>2</v>
+      </c>
+      <c r="L6" s="25"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="26"/>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
@@ -10197,7 +10197,7 @@
       <c r="J7" s="12">
         <v>6</v>
       </c>
-      <c r="K7" s="54">
+      <c r="K7" s="53">
         <v>4</v>
       </c>
       <c r="L7" s="13">
@@ -10643,7 +10643,7 @@
         <v>34</v>
       </c>
       <c r="B15" s="12"/>
-      <c r="C15" s="54">
+      <c r="C15" s="53">
         <v>3</v>
       </c>
       <c r="D15" s="12">
@@ -10655,7 +10655,7 @@
       <c r="F15" s="12">
         <v>3</v>
       </c>
-      <c r="G15" s="54">
+      <c r="G15" s="53">
         <v>3</v>
       </c>
       <c r="H15" s="12">
@@ -10667,7 +10667,7 @@
       <c r="J15" s="12">
         <v>5</v>
       </c>
-      <c r="K15" s="54">
+      <c r="K15" s="53">
         <v>4</v>
       </c>
       <c r="L15" s="13">
@@ -11018,7 +11018,7 @@
       <c r="J21" s="12">
         <v>5</v>
       </c>
-      <c r="K21" s="54">
+      <c r="K21" s="53">
         <v>4</v>
       </c>
       <c r="L21" s="13">
@@ -11724,23 +11724,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
+      <c r="A1" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -11754,23 +11754,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="57" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
+      <c r="A2" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -11812,49 +11812,49 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="20">
-        <v>1</v>
-      </c>
-      <c r="D4" s="20">
-        <v>2</v>
-      </c>
-      <c r="E4" s="20">
-        <v>3</v>
-      </c>
-      <c r="F4" s="20">
-        <v>4</v>
-      </c>
-      <c r="G4" s="20">
-        <v>5</v>
-      </c>
-      <c r="H4" s="20">
-        <v>6</v>
-      </c>
-      <c r="I4" s="20">
+      <c r="A4" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="19">
+        <v>1</v>
+      </c>
+      <c r="D4" s="19">
+        <v>2</v>
+      </c>
+      <c r="E4" s="19">
+        <v>3</v>
+      </c>
+      <c r="F4" s="19">
+        <v>4</v>
+      </c>
+      <c r="G4" s="19">
+        <v>5</v>
+      </c>
+      <c r="H4" s="19">
+        <v>6</v>
+      </c>
+      <c r="I4" s="19">
         <v>7</v>
       </c>
-      <c r="J4" s="20">
+      <c r="J4" s="19">
         <v>8</v>
       </c>
-      <c r="K4" s="20">
+      <c r="K4" s="19">
         <v>9</v>
       </c>
-      <c r="L4" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="M4" s="20" t="s">
+      <c r="L4" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="M4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="N4" s="20" t="s">
+      <c r="N4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="O4" s="21" t="s">
+      <c r="O4" s="20" t="s">
         <v>9</v>
       </c>
       <c r="P4" s="3"/>
@@ -11870,7 +11870,7 @@
       <c r="Z4" s="3"/>
     </row>
     <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A5" s="22"/>
+      <c r="A5" s="21"/>
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -11907,7 +11907,7 @@
       </c>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
-      <c r="O5" s="23"/>
+      <c r="O5" s="22"/>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
@@ -11921,41 +11921,41 @@
       <c r="Z5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24"/>
-      <c r="B6" s="25" t="s">
+      <c r="A6" s="23"/>
+      <c r="B6" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="25">
-        <v>4</v>
-      </c>
-      <c r="D6" s="25">
-        <v>1</v>
-      </c>
-      <c r="E6" s="25">
-        <v>3</v>
-      </c>
-      <c r="F6" s="25">
+      <c r="C6" s="24">
+        <v>4</v>
+      </c>
+      <c r="D6" s="24">
+        <v>1</v>
+      </c>
+      <c r="E6" s="24">
+        <v>3</v>
+      </c>
+      <c r="F6" s="24">
         <v>9</v>
       </c>
-      <c r="G6" s="25">
-        <v>5</v>
-      </c>
-      <c r="H6" s="25">
+      <c r="G6" s="24">
+        <v>5</v>
+      </c>
+      <c r="H6" s="24">
         <v>7</v>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="24">
         <v>8</v>
       </c>
-      <c r="J6" s="25">
-        <v>6</v>
-      </c>
-      <c r="K6" s="25">
-        <v>2</v>
-      </c>
-      <c r="L6" s="26"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="27"/>
+      <c r="J6" s="24">
+        <v>6</v>
+      </c>
+      <c r="K6" s="24">
+        <v>2</v>
+      </c>
+      <c r="L6" s="25"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="26"/>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
@@ -11987,7 +11987,7 @@
       <c r="F7" s="12">
         <v>3</v>
       </c>
-      <c r="G7" s="54">
+      <c r="G7" s="53">
         <v>3</v>
       </c>
       <c r="H7" s="12">
@@ -12925,7 +12925,7 @@
       <c r="F23" s="12">
         <v>4</v>
       </c>
-      <c r="G23" s="54">
+      <c r="G23" s="53">
         <v>3</v>
       </c>
       <c r="H23" s="12">
@@ -13476,23 +13476,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
+      <c r="A1" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -13506,23 +13506,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="57" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
+      <c r="A2" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -13564,49 +13564,49 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="20">
-        <v>1</v>
-      </c>
-      <c r="D4" s="20">
-        <v>2</v>
-      </c>
-      <c r="E4" s="20">
-        <v>3</v>
-      </c>
-      <c r="F4" s="20">
-        <v>4</v>
-      </c>
-      <c r="G4" s="20">
-        <v>5</v>
-      </c>
-      <c r="H4" s="20">
-        <v>6</v>
-      </c>
-      <c r="I4" s="20">
+      <c r="A4" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="19">
+        <v>1</v>
+      </c>
+      <c r="D4" s="19">
+        <v>2</v>
+      </c>
+      <c r="E4" s="19">
+        <v>3</v>
+      </c>
+      <c r="F4" s="19">
+        <v>4</v>
+      </c>
+      <c r="G4" s="19">
+        <v>5</v>
+      </c>
+      <c r="H4" s="19">
+        <v>6</v>
+      </c>
+      <c r="I4" s="19">
         <v>7</v>
       </c>
-      <c r="J4" s="20">
+      <c r="J4" s="19">
         <v>8</v>
       </c>
-      <c r="K4" s="20">
+      <c r="K4" s="19">
         <v>9</v>
       </c>
-      <c r="L4" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="M4" s="20" t="s">
+      <c r="L4" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="M4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="N4" s="20" t="s">
+      <c r="N4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="O4" s="21" t="s">
+      <c r="O4" s="20" t="s">
         <v>9</v>
       </c>
       <c r="P4" s="3"/>
@@ -13622,7 +13622,7 @@
       <c r="Z4" s="3"/>
     </row>
     <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A5" s="22"/>
+      <c r="A5" s="21"/>
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -13659,7 +13659,7 @@
       </c>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
-      <c r="O5" s="23"/>
+      <c r="O5" s="22"/>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
@@ -13673,41 +13673,41 @@
       <c r="Z5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24"/>
-      <c r="B6" s="25" t="s">
+      <c r="A6" s="23"/>
+      <c r="B6" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="25">
-        <v>4</v>
-      </c>
-      <c r="D6" s="25">
-        <v>1</v>
-      </c>
-      <c r="E6" s="25">
-        <v>3</v>
-      </c>
-      <c r="F6" s="25">
+      <c r="C6" s="24">
+        <v>4</v>
+      </c>
+      <c r="D6" s="24">
+        <v>1</v>
+      </c>
+      <c r="E6" s="24">
+        <v>3</v>
+      </c>
+      <c r="F6" s="24">
         <v>9</v>
       </c>
-      <c r="G6" s="25">
-        <v>5</v>
-      </c>
-      <c r="H6" s="25">
+      <c r="G6" s="24">
+        <v>5</v>
+      </c>
+      <c r="H6" s="24">
         <v>7</v>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="24">
         <v>8</v>
       </c>
-      <c r="J6" s="25">
-        <v>6</v>
-      </c>
-      <c r="K6" s="25">
-        <v>2</v>
-      </c>
-      <c r="L6" s="26"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="27"/>
+      <c r="J6" s="24">
+        <v>6</v>
+      </c>
+      <c r="K6" s="24">
+        <v>2</v>
+      </c>
+      <c r="L6" s="25"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="26"/>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
@@ -13849,7 +13849,7 @@
       <c r="C9" s="12">
         <v>6</v>
       </c>
-      <c r="D9" s="54">
+      <c r="D9" s="53">
         <v>4</v>
       </c>
       <c r="E9" s="12">
@@ -13987,7 +13987,7 @@
       <c r="J11" s="12">
         <v>5</v>
       </c>
-      <c r="K11" s="54">
+      <c r="K11" s="53">
         <v>4</v>
       </c>
       <c r="L11" s="13">
@@ -14203,7 +14203,7 @@
       <c r="D15" s="12">
         <v>7</v>
       </c>
-      <c r="E15" s="54">
+      <c r="E15" s="53">
         <v>3</v>
       </c>
       <c r="F15" s="12">
@@ -14923,7 +14923,7 @@
       <c r="J27" s="12">
         <v>5</v>
       </c>
-      <c r="K27" s="54">
+      <c r="K27" s="53">
         <v>4</v>
       </c>
       <c r="L27" s="13">
@@ -15019,7 +15019,7 @@
       <c r="C29" s="12">
         <v>4</v>
       </c>
-      <c r="D29" s="54">
+      <c r="D29" s="53">
         <v>4</v>
       </c>
       <c r="E29" s="12">
@@ -15157,7 +15157,7 @@
       <c r="J31" s="12">
         <v>5</v>
       </c>
-      <c r="K31" s="54">
+      <c r="K31" s="53">
         <v>4</v>
       </c>
       <c r="L31" s="13">
@@ -15278,23 +15278,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
+      <c r="A1" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -15308,23 +15308,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="57" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
+      <c r="A2" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -15366,49 +15366,49 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="20">
-        <v>1</v>
-      </c>
-      <c r="D4" s="20">
-        <v>2</v>
-      </c>
-      <c r="E4" s="20">
-        <v>3</v>
-      </c>
-      <c r="F4" s="20">
-        <v>4</v>
-      </c>
-      <c r="G4" s="20">
-        <v>5</v>
-      </c>
-      <c r="H4" s="20">
-        <v>6</v>
-      </c>
-      <c r="I4" s="20">
+      <c r="A4" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="19">
+        <v>1</v>
+      </c>
+      <c r="D4" s="19">
+        <v>2</v>
+      </c>
+      <c r="E4" s="19">
+        <v>3</v>
+      </c>
+      <c r="F4" s="19">
+        <v>4</v>
+      </c>
+      <c r="G4" s="19">
+        <v>5</v>
+      </c>
+      <c r="H4" s="19">
+        <v>6</v>
+      </c>
+      <c r="I4" s="19">
         <v>7</v>
       </c>
-      <c r="J4" s="20">
+      <c r="J4" s="19">
         <v>8</v>
       </c>
-      <c r="K4" s="20">
+      <c r="K4" s="19">
         <v>9</v>
       </c>
-      <c r="L4" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="M4" s="20" t="s">
+      <c r="L4" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="M4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="N4" s="20" t="s">
+      <c r="N4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="O4" s="21" t="s">
+      <c r="O4" s="20" t="s">
         <v>9</v>
       </c>
       <c r="P4" s="3"/>
@@ -15424,7 +15424,7 @@
       <c r="Z4" s="3"/>
     </row>
     <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A5" s="22"/>
+      <c r="A5" s="21"/>
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -15461,7 +15461,7 @@
       </c>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
-      <c r="O5" s="23"/>
+      <c r="O5" s="22"/>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
@@ -15475,41 +15475,41 @@
       <c r="Z5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24"/>
-      <c r="B6" s="25" t="s">
+      <c r="A6" s="23"/>
+      <c r="B6" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="25">
-        <v>4</v>
-      </c>
-      <c r="D6" s="25">
-        <v>1</v>
-      </c>
-      <c r="E6" s="25">
-        <v>3</v>
-      </c>
-      <c r="F6" s="25">
+      <c r="C6" s="24">
+        <v>4</v>
+      </c>
+      <c r="D6" s="24">
+        <v>1</v>
+      </c>
+      <c r="E6" s="24">
+        <v>3</v>
+      </c>
+      <c r="F6" s="24">
         <v>9</v>
       </c>
-      <c r="G6" s="25">
-        <v>5</v>
-      </c>
-      <c r="H6" s="25">
+      <c r="G6" s="24">
+        <v>5</v>
+      </c>
+      <c r="H6" s="24">
         <v>7</v>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="24">
         <v>8</v>
       </c>
-      <c r="J6" s="25">
-        <v>6</v>
-      </c>
-      <c r="K6" s="25">
-        <v>2</v>
-      </c>
-      <c r="L6" s="26"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="27"/>
+      <c r="J6" s="24">
+        <v>6</v>
+      </c>
+      <c r="K6" s="24">
+        <v>2</v>
+      </c>
+      <c r="L6" s="25"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="26"/>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
@@ -16356,7 +16356,7 @@
       <c r="D21" s="12">
         <v>5</v>
       </c>
-      <c r="E21" s="54">
+      <c r="E21" s="53">
         <v>3</v>
       </c>
       <c r="F21" s="12">
@@ -16485,7 +16485,7 @@
       <c r="H23" s="12">
         <v>4</v>
       </c>
-      <c r="I23" s="54">
+      <c r="I23" s="53">
         <v>2</v>
       </c>
       <c r="J23" s="12">
@@ -18079,23 +18079,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
+      <c r="A1" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -18109,23 +18109,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="57" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
+      <c r="A2" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -18167,49 +18167,49 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="20">
-        <v>1</v>
-      </c>
-      <c r="D4" s="20">
-        <v>2</v>
-      </c>
-      <c r="E4" s="20">
-        <v>3</v>
-      </c>
-      <c r="F4" s="20">
-        <v>4</v>
-      </c>
-      <c r="G4" s="20">
-        <v>5</v>
-      </c>
-      <c r="H4" s="20">
-        <v>6</v>
-      </c>
-      <c r="I4" s="20">
+      <c r="A4" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="19">
+        <v>1</v>
+      </c>
+      <c r="D4" s="19">
+        <v>2</v>
+      </c>
+      <c r="E4" s="19">
+        <v>3</v>
+      </c>
+      <c r="F4" s="19">
+        <v>4</v>
+      </c>
+      <c r="G4" s="19">
+        <v>5</v>
+      </c>
+      <c r="H4" s="19">
+        <v>6</v>
+      </c>
+      <c r="I4" s="19">
         <v>7</v>
       </c>
-      <c r="J4" s="20">
+      <c r="J4" s="19">
         <v>8</v>
       </c>
-      <c r="K4" s="20">
+      <c r="K4" s="19">
         <v>9</v>
       </c>
-      <c r="L4" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="M4" s="20" t="s">
+      <c r="L4" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="M4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="N4" s="20" t="s">
+      <c r="N4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="O4" s="21" t="s">
+      <c r="O4" s="20" t="s">
         <v>9</v>
       </c>
       <c r="P4" s="3"/>
@@ -18225,7 +18225,7 @@
       <c r="Z4" s="3"/>
     </row>
     <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A5" s="22"/>
+      <c r="A5" s="21"/>
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -18262,7 +18262,7 @@
       </c>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
-      <c r="O5" s="23"/>
+      <c r="O5" s="22"/>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
@@ -18276,41 +18276,41 @@
       <c r="Z5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24"/>
-      <c r="B6" s="25" t="s">
+      <c r="A6" s="23"/>
+      <c r="B6" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="25">
-        <v>4</v>
-      </c>
-      <c r="D6" s="25">
-        <v>1</v>
-      </c>
-      <c r="E6" s="25">
-        <v>3</v>
-      </c>
-      <c r="F6" s="25">
+      <c r="C6" s="24">
+        <v>4</v>
+      </c>
+      <c r="D6" s="24">
+        <v>1</v>
+      </c>
+      <c r="E6" s="24">
+        <v>3</v>
+      </c>
+      <c r="F6" s="24">
         <v>9</v>
       </c>
-      <c r="G6" s="25">
-        <v>5</v>
-      </c>
-      <c r="H6" s="25">
+      <c r="G6" s="24">
+        <v>5</v>
+      </c>
+      <c r="H6" s="24">
         <v>7</v>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="24">
         <v>8</v>
       </c>
-      <c r="J6" s="25">
-        <v>6</v>
-      </c>
-      <c r="K6" s="25">
-        <v>2</v>
-      </c>
-      <c r="L6" s="26"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="27"/>
+      <c r="J6" s="24">
+        <v>6</v>
+      </c>
+      <c r="K6" s="24">
+        <v>2</v>
+      </c>
+      <c r="L6" s="25"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="26"/>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
@@ -19029,23 +19029,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
+      <c r="A1" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -19059,23 +19059,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="57" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
+      <c r="A2" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -19117,49 +19117,49 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="20">
-        <v>1</v>
-      </c>
-      <c r="D4" s="20">
-        <v>2</v>
-      </c>
-      <c r="E4" s="20">
-        <v>3</v>
-      </c>
-      <c r="F4" s="20">
-        <v>4</v>
-      </c>
-      <c r="G4" s="20">
-        <v>5</v>
-      </c>
-      <c r="H4" s="20">
-        <v>6</v>
-      </c>
-      <c r="I4" s="20">
+      <c r="A4" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="19">
+        <v>1</v>
+      </c>
+      <c r="D4" s="19">
+        <v>2</v>
+      </c>
+      <c r="E4" s="19">
+        <v>3</v>
+      </c>
+      <c r="F4" s="19">
+        <v>4</v>
+      </c>
+      <c r="G4" s="19">
+        <v>5</v>
+      </c>
+      <c r="H4" s="19">
+        <v>6</v>
+      </c>
+      <c r="I4" s="19">
         <v>7</v>
       </c>
-      <c r="J4" s="20">
+      <c r="J4" s="19">
         <v>8</v>
       </c>
-      <c r="K4" s="20">
+      <c r="K4" s="19">
         <v>9</v>
       </c>
-      <c r="L4" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="M4" s="20" t="s">
+      <c r="L4" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="M4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="N4" s="20" t="s">
+      <c r="N4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="O4" s="21" t="s">
+      <c r="O4" s="20" t="s">
         <v>9</v>
       </c>
       <c r="P4" s="3"/>
@@ -19175,7 +19175,7 @@
       <c r="Z4" s="3"/>
     </row>
     <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A5" s="22"/>
+      <c r="A5" s="21"/>
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -19212,7 +19212,7 @@
       </c>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
-      <c r="O5" s="23"/>
+      <c r="O5" s="22"/>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
@@ -19226,41 +19226,41 @@
       <c r="Z5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24"/>
-      <c r="B6" s="25" t="s">
+      <c r="A6" s="23"/>
+      <c r="B6" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="25">
-        <v>4</v>
-      </c>
-      <c r="D6" s="25">
-        <v>1</v>
-      </c>
-      <c r="E6" s="25">
-        <v>3</v>
-      </c>
-      <c r="F6" s="25">
+      <c r="C6" s="24">
+        <v>4</v>
+      </c>
+      <c r="D6" s="24">
+        <v>1</v>
+      </c>
+      <c r="E6" s="24">
+        <v>3</v>
+      </c>
+      <c r="F6" s="24">
         <v>9</v>
       </c>
-      <c r="G6" s="25">
-        <v>5</v>
-      </c>
-      <c r="H6" s="25">
+      <c r="G6" s="24">
+        <v>5</v>
+      </c>
+      <c r="H6" s="24">
         <v>7</v>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="24">
         <v>8</v>
       </c>
-      <c r="J6" s="25">
-        <v>6</v>
-      </c>
-      <c r="K6" s="25">
-        <v>2</v>
-      </c>
-      <c r="L6" s="26"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="27"/>
+      <c r="J6" s="24">
+        <v>6</v>
+      </c>
+      <c r="K6" s="24">
+        <v>2</v>
+      </c>
+      <c r="L6" s="25"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="26"/>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
@@ -20711,23 +20711,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
+      <c r="A1" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -20741,23 +20741,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="57" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
+      <c r="A2" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -20799,49 +20799,49 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="20">
-        <v>1</v>
-      </c>
-      <c r="D4" s="20">
-        <v>2</v>
-      </c>
-      <c r="E4" s="20">
-        <v>3</v>
-      </c>
-      <c r="F4" s="20">
-        <v>4</v>
-      </c>
-      <c r="G4" s="20">
-        <v>5</v>
-      </c>
-      <c r="H4" s="20">
-        <v>6</v>
-      </c>
-      <c r="I4" s="20">
+      <c r="A4" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="19">
+        <v>1</v>
+      </c>
+      <c r="D4" s="19">
+        <v>2</v>
+      </c>
+      <c r="E4" s="19">
+        <v>3</v>
+      </c>
+      <c r="F4" s="19">
+        <v>4</v>
+      </c>
+      <c r="G4" s="19">
+        <v>5</v>
+      </c>
+      <c r="H4" s="19">
+        <v>6</v>
+      </c>
+      <c r="I4" s="19">
         <v>7</v>
       </c>
-      <c r="J4" s="20">
+      <c r="J4" s="19">
         <v>8</v>
       </c>
-      <c r="K4" s="20">
+      <c r="K4" s="19">
         <v>9</v>
       </c>
-      <c r="L4" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="M4" s="20" t="s">
+      <c r="L4" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="M4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="N4" s="20" t="s">
+      <c r="N4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="O4" s="21" t="s">
+      <c r="O4" s="20" t="s">
         <v>9</v>
       </c>
       <c r="P4" s="3"/>
@@ -20857,7 +20857,7 @@
       <c r="Z4" s="3"/>
     </row>
     <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A5" s="22"/>
+      <c r="A5" s="21"/>
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
-      <c r="O5" s="23"/>
+      <c r="O5" s="22"/>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
@@ -20908,41 +20908,41 @@
       <c r="Z5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24"/>
-      <c r="B6" s="25" t="s">
+      <c r="A6" s="23"/>
+      <c r="B6" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="25">
-        <v>4</v>
-      </c>
-      <c r="D6" s="25">
-        <v>1</v>
-      </c>
-      <c r="E6" s="25">
-        <v>3</v>
-      </c>
-      <c r="F6" s="25">
+      <c r="C6" s="24">
+        <v>4</v>
+      </c>
+      <c r="D6" s="24">
+        <v>1</v>
+      </c>
+      <c r="E6" s="24">
+        <v>3</v>
+      </c>
+      <c r="F6" s="24">
         <v>9</v>
       </c>
-      <c r="G6" s="25">
-        <v>5</v>
-      </c>
-      <c r="H6" s="25">
+      <c r="G6" s="24">
+        <v>5</v>
+      </c>
+      <c r="H6" s="24">
         <v>7</v>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="24">
         <v>8</v>
       </c>
-      <c r="J6" s="25">
-        <v>6</v>
-      </c>
-      <c r="K6" s="25">
-        <v>2</v>
-      </c>
-      <c r="L6" s="26"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="27"/>
+      <c r="J6" s="24">
+        <v>6</v>
+      </c>
+      <c r="K6" s="24">
+        <v>2</v>
+      </c>
+      <c r="L6" s="25"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="26"/>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
@@ -21649,323 +21649,323 @@
   <dimension ref="A1:Z10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="76" customWidth="1"/>
-    <col min="2" max="2" width="9.1640625" style="35" bestFit="1" customWidth="1"/>
-    <col min="3" max="11" width="5" style="35" customWidth="1"/>
-    <col min="12" max="12" width="5.1640625" style="35" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.1640625" style="35" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5" style="35" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.5" style="35" customWidth="1"/>
-    <col min="16" max="26" width="8.6640625" style="35" customWidth="1"/>
-    <col min="27" max="16384" width="14.1640625" style="35"/>
+    <col min="1" max="1" width="14.6640625" style="73" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" style="34" bestFit="1" customWidth="1"/>
+    <col min="3" max="11" width="5" style="34" customWidth="1"/>
+    <col min="12" max="12" width="5.1640625" style="34" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.1640625" style="34" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5" style="34" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.5" style="34" customWidth="1"/>
+    <col min="16" max="26" width="8.6640625" style="34" customWidth="1"/>
+    <col min="27" max="16384" width="14.1640625" style="34"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="17" x14ac:dyDescent="0.3">
-      <c r="A1" s="58" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="59"/>
-      <c r="N1" s="59"/>
-      <c r="O1" s="59"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="36"/>
-      <c r="R1" s="36"/>
-      <c r="S1" s="36"/>
-      <c r="T1" s="36"/>
-      <c r="U1" s="36"/>
-      <c r="V1" s="36"/>
-      <c r="W1" s="36"/>
-      <c r="X1" s="36"/>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="36"/>
+      <c r="A1" s="57" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
+      <c r="L1" s="58"/>
+      <c r="M1" s="58"/>
+      <c r="N1" s="58"/>
+      <c r="O1" s="58"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="35"/>
+      <c r="V1" s="35"/>
+      <c r="W1" s="35"/>
+      <c r="X1" s="35"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="60" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="59"/>
-      <c r="N2" s="59"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="36"/>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
-      <c r="T2" s="36"/>
-      <c r="U2" s="36"/>
-      <c r="V2" s="36"/>
-      <c r="W2" s="36"/>
-      <c r="X2" s="36"/>
-      <c r="Y2" s="36"/>
-      <c r="Z2" s="36"/>
+      <c r="A2" s="59" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
+      <c r="M2" s="58"/>
+      <c r="N2" s="58"/>
+      <c r="O2" s="58"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="35"/>
+      <c r="W2" s="35"/>
+      <c r="X2" s="35"/>
+      <c r="Y2" s="35"/>
+      <c r="Z2" s="35"/>
     </row>
     <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="70"/>
-      <c r="B3" s="36"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="38"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="38"/>
-      <c r="N3" s="38"/>
-      <c r="O3" s="39"/>
-      <c r="P3" s="36"/>
-      <c r="Q3" s="36"/>
-      <c r="R3" s="36"/>
-      <c r="S3" s="36"/>
-      <c r="T3" s="36"/>
-      <c r="U3" s="36"/>
-      <c r="V3" s="36"/>
-      <c r="W3" s="36"/>
-      <c r="X3" s="36"/>
-      <c r="Y3" s="36"/>
-      <c r="Z3" s="36"/>
+      <c r="A3" s="69"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="37"/>
+      <c r="K3" s="37"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="37"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="38"/>
+      <c r="P3" s="35"/>
+      <c r="Q3" s="35"/>
+      <c r="R3" s="35"/>
+      <c r="S3" s="35"/>
+      <c r="T3" s="35"/>
+      <c r="U3" s="35"/>
+      <c r="V3" s="35"/>
+      <c r="W3" s="35"/>
+      <c r="X3" s="35"/>
+      <c r="Y3" s="35"/>
+      <c r="Z3" s="35"/>
     </row>
     <row r="4" spans="1:26" ht="40" x14ac:dyDescent="0.2">
-      <c r="A4" s="71" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="40" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="40">
-        <v>1</v>
-      </c>
-      <c r="D4" s="40">
-        <v>2</v>
-      </c>
-      <c r="E4" s="40">
-        <v>3</v>
-      </c>
-      <c r="F4" s="40">
-        <v>4</v>
-      </c>
-      <c r="G4" s="40">
-        <v>5</v>
-      </c>
-      <c r="H4" s="40">
-        <v>6</v>
-      </c>
-      <c r="I4" s="40">
+      <c r="A4" s="70" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="39">
+        <v>1</v>
+      </c>
+      <c r="D4" s="39">
+        <v>2</v>
+      </c>
+      <c r="E4" s="39">
+        <v>3</v>
+      </c>
+      <c r="F4" s="39">
+        <v>4</v>
+      </c>
+      <c r="G4" s="39">
+        <v>5</v>
+      </c>
+      <c r="H4" s="39">
+        <v>6</v>
+      </c>
+      <c r="I4" s="39">
         <v>7</v>
       </c>
-      <c r="J4" s="40">
+      <c r="J4" s="39">
         <v>8</v>
       </c>
-      <c r="K4" s="40">
+      <c r="K4" s="39">
         <v>9</v>
       </c>
-      <c r="L4" s="40" t="s">
-        <v>6</v>
-      </c>
-      <c r="M4" s="40" t="s">
+      <c r="L4" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="M4" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="N4" s="40" t="s">
+      <c r="N4" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="O4" s="41" t="s">
+      <c r="O4" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="P4" s="37"/>
-      <c r="Q4" s="37"/>
-      <c r="R4" s="37"/>
-      <c r="S4" s="37"/>
-      <c r="T4" s="37"/>
-      <c r="U4" s="37"/>
-      <c r="V4" s="37"/>
-      <c r="W4" s="37"/>
-      <c r="X4" s="37"/>
-      <c r="Y4" s="37"/>
-      <c r="Z4" s="37"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
+      <c r="S4" s="36"/>
+      <c r="T4" s="36"/>
+      <c r="U4" s="36"/>
+      <c r="V4" s="36"/>
+      <c r="W4" s="36"/>
+      <c r="X4" s="36"/>
+      <c r="Y4" s="36"/>
+      <c r="Z4" s="36"/>
     </row>
     <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A5" s="72"/>
-      <c r="B5" s="42" t="s">
+      <c r="A5" s="71"/>
+      <c r="B5" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="42">
-        <v>4</v>
-      </c>
-      <c r="D5" s="42">
-        <v>5</v>
-      </c>
-      <c r="E5" s="42">
-        <v>4</v>
-      </c>
-      <c r="F5" s="42">
-        <v>3</v>
-      </c>
-      <c r="G5" s="42">
-        <v>4</v>
-      </c>
-      <c r="H5" s="42">
-        <v>4</v>
-      </c>
-      <c r="I5" s="42">
-        <v>3</v>
-      </c>
-      <c r="J5" s="42">
-        <v>4</v>
-      </c>
-      <c r="K5" s="42">
-        <v>5</v>
-      </c>
-      <c r="L5" s="43">
+      <c r="C5" s="41">
+        <v>4</v>
+      </c>
+      <c r="D5" s="41">
+        <v>5</v>
+      </c>
+      <c r="E5" s="41">
+        <v>4</v>
+      </c>
+      <c r="F5" s="41">
+        <v>3</v>
+      </c>
+      <c r="G5" s="41">
+        <v>4</v>
+      </c>
+      <c r="H5" s="41">
+        <v>4</v>
+      </c>
+      <c r="I5" s="41">
+        <v>3</v>
+      </c>
+      <c r="J5" s="41">
+        <v>4</v>
+      </c>
+      <c r="K5" s="41">
+        <v>5</v>
+      </c>
+      <c r="L5" s="42">
         <f>SUM(C5:K5)</f>
         <v>36</v>
       </c>
-      <c r="M5" s="42"/>
-      <c r="N5" s="42"/>
-      <c r="O5" s="44"/>
-      <c r="P5" s="37"/>
-      <c r="Q5" s="37"/>
-      <c r="R5" s="37"/>
-      <c r="S5" s="37"/>
-      <c r="T5" s="37"/>
-      <c r="U5" s="37"/>
-      <c r="V5" s="37"/>
-      <c r="W5" s="37"/>
-      <c r="X5" s="37"/>
-      <c r="Y5" s="37"/>
-      <c r="Z5" s="37"/>
+      <c r="M5" s="41"/>
+      <c r="N5" s="41"/>
+      <c r="O5" s="43"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
+      <c r="S5" s="36"/>
+      <c r="T5" s="36"/>
+      <c r="U5" s="36"/>
+      <c r="V5" s="36"/>
+      <c r="W5" s="36"/>
+      <c r="X5" s="36"/>
+      <c r="Y5" s="36"/>
+      <c r="Z5" s="36"/>
     </row>
     <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="73"/>
-      <c r="B6" s="45" t="s">
+      <c r="A6" s="72"/>
+      <c r="B6" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="45">
-        <v>4</v>
-      </c>
-      <c r="D6" s="45">
-        <v>1</v>
-      </c>
-      <c r="E6" s="45">
-        <v>3</v>
-      </c>
-      <c r="F6" s="45">
+      <c r="C6" s="44">
+        <v>4</v>
+      </c>
+      <c r="D6" s="44">
+        <v>1</v>
+      </c>
+      <c r="E6" s="44">
+        <v>3</v>
+      </c>
+      <c r="F6" s="44">
         <v>9</v>
       </c>
-      <c r="G6" s="45">
-        <v>5</v>
-      </c>
-      <c r="H6" s="45">
+      <c r="G6" s="44">
+        <v>5</v>
+      </c>
+      <c r="H6" s="44">
         <v>7</v>
       </c>
-      <c r="I6" s="45">
+      <c r="I6" s="44">
         <v>8</v>
       </c>
-      <c r="J6" s="45">
-        <v>6</v>
-      </c>
-      <c r="K6" s="45">
-        <v>2</v>
-      </c>
-      <c r="L6" s="46"/>
-      <c r="M6" s="45"/>
-      <c r="N6" s="45"/>
-      <c r="O6" s="47"/>
-      <c r="P6" s="37"/>
-      <c r="Q6" s="37"/>
-      <c r="R6" s="37"/>
-      <c r="S6" s="37"/>
-      <c r="T6" s="37"/>
-      <c r="U6" s="37"/>
-      <c r="V6" s="37"/>
-      <c r="W6" s="37"/>
-      <c r="X6" s="37"/>
-      <c r="Y6" s="37"/>
-      <c r="Z6" s="37"/>
+      <c r="J6" s="44">
+        <v>6</v>
+      </c>
+      <c r="K6" s="44">
+        <v>2</v>
+      </c>
+      <c r="L6" s="45"/>
+      <c r="M6" s="44"/>
+      <c r="N6" s="44"/>
+      <c r="O6" s="46"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
+      <c r="S6" s="36"/>
+      <c r="T6" s="36"/>
+      <c r="U6" s="36"/>
+      <c r="V6" s="36"/>
+      <c r="W6" s="36"/>
+      <c r="X6" s="36"/>
+      <c r="Y6" s="36"/>
+      <c r="Z6" s="36"/>
     </row>
     <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A7" s="74" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="48" t="s">
+      <c r="B7" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="48">
+      <c r="C7" s="47">
         <v>7</v>
       </c>
-      <c r="D7" s="48">
-        <v>6</v>
-      </c>
-      <c r="E7" s="48">
-        <v>6</v>
-      </c>
-      <c r="F7" s="48">
-        <v>3</v>
-      </c>
-      <c r="G7" s="48">
+      <c r="D7" s="47">
+        <v>6</v>
+      </c>
+      <c r="E7" s="47">
+        <v>6</v>
+      </c>
+      <c r="F7" s="47">
+        <v>3</v>
+      </c>
+      <c r="G7" s="47">
         <v>7</v>
       </c>
-      <c r="H7" s="48">
+      <c r="H7" s="47">
         <v>8</v>
       </c>
-      <c r="I7" s="48">
-        <v>4</v>
-      </c>
-      <c r="J7" s="48">
-        <v>6</v>
-      </c>
-      <c r="K7" s="48">
+      <c r="I7" s="47">
+        <v>4</v>
+      </c>
+      <c r="J7" s="47">
+        <v>6</v>
+      </c>
+      <c r="K7" s="47">
         <v>9</v>
       </c>
-      <c r="L7" s="49">
+      <c r="L7" s="48">
         <f t="shared" ref="L7:L10" si="0">IF(SUM(C7:K7)&gt;0, SUM(C7:K7),"")</f>
         <v>56</v>
       </c>
-      <c r="M7" s="48">
+      <c r="M7" s="47">
         <v>21</v>
       </c>
-      <c r="N7" s="48">
+      <c r="N7" s="47">
         <f>IF(L7&lt;&gt;"",L7- M7, "")</f>
         <v>35</v>
       </c>
-      <c r="O7" s="50"/>
-      <c r="P7" s="36"/>
-      <c r="Q7" s="36"/>
-      <c r="R7" s="36"/>
-      <c r="S7" s="36"/>
-      <c r="T7" s="36"/>
-      <c r="U7" s="36"/>
-      <c r="V7" s="36"/>
-      <c r="W7" s="36"/>
-      <c r="X7" s="36"/>
-      <c r="Y7" s="36"/>
-      <c r="Z7" s="36"/>
+      <c r="O7" s="49"/>
+      <c r="P7" s="35"/>
+      <c r="Q7" s="35"/>
+      <c r="R7" s="35"/>
+      <c r="S7" s="35"/>
+      <c r="T7" s="35"/>
+      <c r="U7" s="35"/>
+      <c r="V7" s="35"/>
+      <c r="W7" s="35"/>
+      <c r="X7" s="35"/>
+      <c r="Y7" s="35"/>
+      <c r="Z7" s="35"/>
     </row>
     <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="75"/>
-      <c r="B8" s="51" t="s">
+      <c r="B8" s="50" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="16">
@@ -22004,87 +22004,87 @@
         <f>IF(K7&gt;0, VLOOKUP(K7-K$5-(INT($M7/9)+(MOD($M7,9)&gt;=K$6)), 'Point System'!$A$4:$B$15, 2),"")</f>
         <v>1</v>
       </c>
-      <c r="L8" s="52">
+      <c r="L8" s="51">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="M8" s="51"/>
-      <c r="N8" s="51"/>
-      <c r="O8" s="53">
+      <c r="M8" s="50"/>
+      <c r="N8" s="50"/>
+      <c r="O8" s="52">
         <f>IF(L8&lt;&gt;"", L8, "")</f>
         <v>19</v>
       </c>
-      <c r="P8" s="36"/>
-      <c r="Q8" s="36"/>
-      <c r="R8" s="36"/>
-      <c r="S8" s="36"/>
-      <c r="T8" s="36"/>
-      <c r="U8" s="36"/>
-      <c r="V8" s="36"/>
-      <c r="W8" s="36"/>
-      <c r="X8" s="36"/>
-      <c r="Y8" s="36"/>
-      <c r="Z8" s="36"/>
+      <c r="P8" s="35"/>
+      <c r="Q8" s="35"/>
+      <c r="R8" s="35"/>
+      <c r="S8" s="35"/>
+      <c r="T8" s="35"/>
+      <c r="U8" s="35"/>
+      <c r="V8" s="35"/>
+      <c r="W8" s="35"/>
+      <c r="X8" s="35"/>
+      <c r="Y8" s="35"/>
+      <c r="Z8" s="35"/>
     </row>
     <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A9" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="48"/>
-      <c r="C9" s="48">
-        <v>6</v>
-      </c>
-      <c r="D9" s="48">
-        <v>6</v>
-      </c>
-      <c r="E9" s="48">
-        <v>6</v>
-      </c>
-      <c r="F9" s="48">
-        <v>4</v>
-      </c>
-      <c r="G9" s="48">
-        <v>6</v>
-      </c>
-      <c r="H9" s="48">
+      <c r="B9" s="47"/>
+      <c r="C9" s="47">
+        <v>6</v>
+      </c>
+      <c r="D9" s="47">
+        <v>6</v>
+      </c>
+      <c r="E9" s="47">
+        <v>6</v>
+      </c>
+      <c r="F9" s="47">
+        <v>4</v>
+      </c>
+      <c r="G9" s="47">
+        <v>6</v>
+      </c>
+      <c r="H9" s="47">
         <v>7</v>
       </c>
-      <c r="I9" s="48">
-        <v>4</v>
-      </c>
-      <c r="J9" s="48">
-        <v>6</v>
-      </c>
-      <c r="K9" s="48">
+      <c r="I9" s="47">
+        <v>4</v>
+      </c>
+      <c r="J9" s="47">
+        <v>6</v>
+      </c>
+      <c r="K9" s="47">
         <v>7</v>
       </c>
-      <c r="L9" s="49">
+      <c r="L9" s="48">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="M9" s="48">
+      <c r="M9" s="47">
         <v>15</v>
       </c>
-      <c r="N9" s="48">
+      <c r="N9" s="47">
         <f>IF(L9&lt;&gt;"",L9- M9, "")</f>
         <v>37</v>
       </c>
-      <c r="O9" s="50"/>
-      <c r="P9" s="36"/>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="36"/>
-      <c r="S9" s="36"/>
-      <c r="T9" s="36"/>
-      <c r="U9" s="36"/>
-      <c r="V9" s="36"/>
-      <c r="W9" s="36"/>
-      <c r="X9" s="36"/>
-      <c r="Y9" s="36"/>
-      <c r="Z9" s="36"/>
+      <c r="O9" s="49"/>
+      <c r="P9" s="35"/>
+      <c r="Q9" s="35"/>
+      <c r="R9" s="35"/>
+      <c r="S9" s="35"/>
+      <c r="T9" s="35"/>
+      <c r="U9" s="35"/>
+      <c r="V9" s="35"/>
+      <c r="W9" s="35"/>
+      <c r="X9" s="35"/>
+      <c r="Y9" s="35"/>
+      <c r="Z9" s="35"/>
     </row>
     <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="75"/>
-      <c r="B10" s="51"/>
+      <c r="B10" s="50"/>
       <c r="C10" s="16">
         <f>IF(C9&gt;0, VLOOKUP(C9-C$5-(INT($M9/9)+(MOD($M9,9)&gt;=C$6)), 'Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
@@ -22121,27 +22121,27 @@
         <f>IF(K9&gt;0, VLOOKUP(K9-K$5-(INT($M9/9)+(MOD($M9,9)&gt;=K$6)), 'Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
-      <c r="L10" s="52">
+      <c r="L10" s="51">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="M10" s="51"/>
-      <c r="N10" s="51"/>
-      <c r="O10" s="53">
+      <c r="M10" s="50"/>
+      <c r="N10" s="50"/>
+      <c r="O10" s="52">
         <f>IF(L10&lt;&gt;"", L10, "")</f>
         <v>17</v>
       </c>
-      <c r="P10" s="36"/>
-      <c r="Q10" s="36"/>
-      <c r="R10" s="36"/>
-      <c r="S10" s="36"/>
-      <c r="T10" s="36"/>
-      <c r="U10" s="36"/>
-      <c r="V10" s="36"/>
-      <c r="W10" s="36"/>
-      <c r="X10" s="36"/>
-      <c r="Y10" s="36"/>
-      <c r="Z10" s="36"/>
+      <c r="P10" s="35"/>
+      <c r="Q10" s="35"/>
+      <c r="R10" s="35"/>
+      <c r="S10" s="35"/>
+      <c r="T10" s="35"/>
+      <c r="U10" s="35"/>
+      <c r="V10" s="35"/>
+      <c r="W10" s="35"/>
+      <c r="X10" s="35"/>
+      <c r="Y10" s="35"/>
+      <c r="Z10" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -22173,23 +22173,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
+      <c r="A1" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -22203,23 +22203,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="57" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
+      <c r="A2" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -22261,49 +22261,49 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="20">
-        <v>1</v>
-      </c>
-      <c r="D4" s="20">
-        <v>2</v>
-      </c>
-      <c r="E4" s="20">
-        <v>3</v>
-      </c>
-      <c r="F4" s="20">
-        <v>4</v>
-      </c>
-      <c r="G4" s="20">
-        <v>5</v>
-      </c>
-      <c r="H4" s="20">
-        <v>6</v>
-      </c>
-      <c r="I4" s="20">
+      <c r="A4" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="19">
+        <v>1</v>
+      </c>
+      <c r="D4" s="19">
+        <v>2</v>
+      </c>
+      <c r="E4" s="19">
+        <v>3</v>
+      </c>
+      <c r="F4" s="19">
+        <v>4</v>
+      </c>
+      <c r="G4" s="19">
+        <v>5</v>
+      </c>
+      <c r="H4" s="19">
+        <v>6</v>
+      </c>
+      <c r="I4" s="19">
         <v>7</v>
       </c>
-      <c r="J4" s="20">
+      <c r="J4" s="19">
         <v>8</v>
       </c>
-      <c r="K4" s="20">
+      <c r="K4" s="19">
         <v>9</v>
       </c>
-      <c r="L4" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="M4" s="20" t="s">
+      <c r="L4" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="M4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="N4" s="20" t="s">
+      <c r="N4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="O4" s="21" t="s">
+      <c r="O4" s="20" t="s">
         <v>9</v>
       </c>
       <c r="P4" s="3"/>
@@ -22319,7 +22319,7 @@
       <c r="Z4" s="3"/>
     </row>
     <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A5" s="22"/>
+      <c r="A5" s="21"/>
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -22356,7 +22356,7 @@
       </c>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
-      <c r="O5" s="23"/>
+      <c r="O5" s="22"/>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
@@ -22370,41 +22370,41 @@
       <c r="Z5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24"/>
-      <c r="B6" s="25" t="s">
+      <c r="A6" s="23"/>
+      <c r="B6" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="25">
-        <v>4</v>
-      </c>
-      <c r="D6" s="25">
-        <v>1</v>
-      </c>
-      <c r="E6" s="25">
-        <v>3</v>
-      </c>
-      <c r="F6" s="25">
+      <c r="C6" s="24">
+        <v>4</v>
+      </c>
+      <c r="D6" s="24">
+        <v>1</v>
+      </c>
+      <c r="E6" s="24">
+        <v>3</v>
+      </c>
+      <c r="F6" s="24">
         <v>9</v>
       </c>
-      <c r="G6" s="25">
-        <v>5</v>
-      </c>
-      <c r="H6" s="25">
+      <c r="G6" s="24">
+        <v>5</v>
+      </c>
+      <c r="H6" s="24">
         <v>7</v>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="24">
         <v>8</v>
       </c>
-      <c r="J6" s="25">
-        <v>6</v>
-      </c>
-      <c r="K6" s="25">
-        <v>2</v>
-      </c>
-      <c r="L6" s="26"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="27"/>
+      <c r="J6" s="24">
+        <v>6</v>
+      </c>
+      <c r="K6" s="24">
+        <v>2</v>
+      </c>
+      <c r="L6" s="25"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="26"/>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
@@ -23237,23 +23237,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
+      <c r="A1" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -23267,23 +23267,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="57" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
+      <c r="A2" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -23325,49 +23325,49 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="20">
-        <v>1</v>
-      </c>
-      <c r="D4" s="20">
-        <v>2</v>
-      </c>
-      <c r="E4" s="20">
-        <v>3</v>
-      </c>
-      <c r="F4" s="20">
-        <v>4</v>
-      </c>
-      <c r="G4" s="20">
-        <v>5</v>
-      </c>
-      <c r="H4" s="20">
-        <v>6</v>
-      </c>
-      <c r="I4" s="20">
+      <c r="A4" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="19">
+        <v>1</v>
+      </c>
+      <c r="D4" s="19">
+        <v>2</v>
+      </c>
+      <c r="E4" s="19">
+        <v>3</v>
+      </c>
+      <c r="F4" s="19">
+        <v>4</v>
+      </c>
+      <c r="G4" s="19">
+        <v>5</v>
+      </c>
+      <c r="H4" s="19">
+        <v>6</v>
+      </c>
+      <c r="I4" s="19">
         <v>7</v>
       </c>
-      <c r="J4" s="20">
+      <c r="J4" s="19">
         <v>8</v>
       </c>
-      <c r="K4" s="20">
+      <c r="K4" s="19">
         <v>9</v>
       </c>
-      <c r="L4" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="M4" s="20" t="s">
+      <c r="L4" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="M4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="N4" s="20" t="s">
+      <c r="N4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="O4" s="21" t="s">
+      <c r="O4" s="20" t="s">
         <v>9</v>
       </c>
       <c r="P4" s="3"/>
@@ -23383,7 +23383,7 @@
       <c r="Z4" s="3"/>
     </row>
     <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A5" s="22"/>
+      <c r="A5" s="21"/>
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -23420,7 +23420,7 @@
       </c>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
-      <c r="O5" s="23"/>
+      <c r="O5" s="22"/>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
@@ -23434,41 +23434,41 @@
       <c r="Z5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24"/>
-      <c r="B6" s="25" t="s">
+      <c r="A6" s="23"/>
+      <c r="B6" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="25">
-        <v>4</v>
-      </c>
-      <c r="D6" s="25">
-        <v>1</v>
-      </c>
-      <c r="E6" s="25">
-        <v>3</v>
-      </c>
-      <c r="F6" s="25">
+      <c r="C6" s="24">
+        <v>4</v>
+      </c>
+      <c r="D6" s="24">
+        <v>1</v>
+      </c>
+      <c r="E6" s="24">
+        <v>3</v>
+      </c>
+      <c r="F6" s="24">
         <v>9</v>
       </c>
-      <c r="G6" s="25">
-        <v>5</v>
-      </c>
-      <c r="H6" s="25">
+      <c r="G6" s="24">
+        <v>5</v>
+      </c>
+      <c r="H6" s="24">
         <v>7</v>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="24">
         <v>8</v>
       </c>
-      <c r="J6" s="25">
-        <v>6</v>
-      </c>
-      <c r="K6" s="25">
-        <v>2</v>
-      </c>
-      <c r="L6" s="26"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="27"/>
+      <c r="J6" s="24">
+        <v>6</v>
+      </c>
+      <c r="K6" s="24">
+        <v>2</v>
+      </c>
+      <c r="L6" s="25"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="26"/>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
@@ -24793,23 +24793,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
+      <c r="A1" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -24823,23 +24823,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="57" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
+      <c r="A2" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -24881,49 +24881,49 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="20">
-        <v>1</v>
-      </c>
-      <c r="D4" s="20">
-        <v>2</v>
-      </c>
-      <c r="E4" s="20">
-        <v>3</v>
-      </c>
-      <c r="F4" s="20">
-        <v>4</v>
-      </c>
-      <c r="G4" s="20">
-        <v>5</v>
-      </c>
-      <c r="H4" s="20">
-        <v>6</v>
-      </c>
-      <c r="I4" s="20">
+      <c r="A4" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="19">
+        <v>1</v>
+      </c>
+      <c r="D4" s="19">
+        <v>2</v>
+      </c>
+      <c r="E4" s="19">
+        <v>3</v>
+      </c>
+      <c r="F4" s="19">
+        <v>4</v>
+      </c>
+      <c r="G4" s="19">
+        <v>5</v>
+      </c>
+      <c r="H4" s="19">
+        <v>6</v>
+      </c>
+      <c r="I4" s="19">
         <v>7</v>
       </c>
-      <c r="J4" s="20">
+      <c r="J4" s="19">
         <v>8</v>
       </c>
-      <c r="K4" s="20">
+      <c r="K4" s="19">
         <v>9</v>
       </c>
-      <c r="L4" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="M4" s="20" t="s">
+      <c r="L4" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="M4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="N4" s="20" t="s">
+      <c r="N4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="O4" s="21" t="s">
+      <c r="O4" s="20" t="s">
         <v>9</v>
       </c>
       <c r="P4" s="3"/>
@@ -24939,7 +24939,7 @@
       <c r="Z4" s="3"/>
     </row>
     <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A5" s="22"/>
+      <c r="A5" s="6"/>
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -24976,7 +24976,7 @@
       </c>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
-      <c r="O5" s="23"/>
+      <c r="O5" s="22"/>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
@@ -24990,41 +24990,41 @@
       <c r="Z5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24"/>
-      <c r="B6" s="25" t="s">
+      <c r="A6" s="23"/>
+      <c r="B6" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="25">
-        <v>4</v>
-      </c>
-      <c r="D6" s="25">
-        <v>1</v>
-      </c>
-      <c r="E6" s="25">
-        <v>3</v>
-      </c>
-      <c r="F6" s="25">
+      <c r="C6" s="24">
+        <v>4</v>
+      </c>
+      <c r="D6" s="24">
+        <v>1</v>
+      </c>
+      <c r="E6" s="24">
+        <v>3</v>
+      </c>
+      <c r="F6" s="24">
         <v>9</v>
       </c>
-      <c r="G6" s="25">
-        <v>5</v>
-      </c>
-      <c r="H6" s="25">
+      <c r="G6" s="24">
+        <v>5</v>
+      </c>
+      <c r="H6" s="24">
         <v>7</v>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="24">
         <v>8</v>
       </c>
-      <c r="J6" s="25">
-        <v>6</v>
-      </c>
-      <c r="K6" s="25">
-        <v>2</v>
-      </c>
-      <c r="L6" s="26"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="27"/>
+      <c r="J6" s="24">
+        <v>6</v>
+      </c>
+      <c r="K6" s="24">
+        <v>2</v>
+      </c>
+      <c r="L6" s="25"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="26"/>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>

--- a/public/results/2025/2025 Weekly Stats - Week 16.xlsx
+++ b/public/results/2025/2025 Weekly Stats - Week 16.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
-  <workbookPr/>
+  <workbookPr updateLinks="always"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mthutter/CODE/golf-league-site/public/results/2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{204337AF-8863-DD46-AF0E-BF0A4C2C9D09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3181B8A7-654A-CA4E-BB38-B19FF68D8EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1300" yWindow="500" windowWidth="28100" windowHeight="19840" firstSheet="3" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1300" yWindow="500" windowWidth="28100" windowHeight="19840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="14" r:id="rId1"/>
@@ -402,7 +402,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -545,28 +545,9 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -605,6 +586,22 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1080,23 +1077,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="54" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
+      <c r="A1" s="68" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -1110,25 +1107,25 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A2" s="56" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
+      <c r="A2" s="70" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
       <c r="T2" s="29"/>
@@ -1155,8 +1152,8 @@
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
       <c r="O3" s="5"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
       <c r="T3" s="29"/>
@@ -1168,7 +1165,7 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.25">
-      <c r="A4" s="64" t="s">
+      <c r="A4" s="55" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="19" t="s">
@@ -1213,8 +1210,8 @@
       <c r="O4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="P4" s="61"/>
-      <c r="Q4" s="62"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="54"/>
       <c r="R4" s="27"/>
       <c r="S4" s="3"/>
       <c r="T4" s="30"/>
@@ -1226,7 +1223,7 @@
       <c r="Z4" s="3"/>
     </row>
     <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A5" s="65"/>
+      <c r="A5" s="56"/>
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -1264,8 +1261,8 @@
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
       <c r="O5" s="22"/>
-      <c r="P5" s="61"/>
-      <c r="Q5" s="63"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="32"/>
       <c r="R5" s="4"/>
       <c r="S5" s="3"/>
       <c r="T5" s="30"/>
@@ -1277,7 +1274,7 @@
       <c r="Z5" s="3"/>
     </row>
     <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="66"/>
+      <c r="A6" s="57"/>
       <c r="B6" s="24" t="s">
         <v>24</v>
       </c>
@@ -1325,7 +1322,7 @@
       <c r="Z6" s="3"/>
     </row>
     <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A7" s="67"/>
+      <c r="A7" s="58"/>
       <c r="B7" s="12" t="s">
         <v>23</v>
       </c>
@@ -1361,7 +1358,7 @@
       <c r="Z7" s="1"/>
     </row>
     <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="68"/>
+      <c r="A8" s="59"/>
       <c r="B8" s="16" t="s">
         <v>25</v>
       </c>
@@ -1423,7 +1420,7 @@
       <c r="Z8" s="33"/>
     </row>
     <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A9" s="67"/>
+      <c r="A9" s="58"/>
       <c r="B9" s="12"/>
       <c r="C9" s="12"/>
       <c r="D9" s="12"/>
@@ -1450,7 +1447,7 @@
       <c r="T9" s="2"/>
     </row>
     <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="68"/>
+      <c r="A10" s="59"/>
       <c r="B10" s="16"/>
       <c r="C10" s="16" t="str">
         <f>IF(C9&gt;0, VLOOKUP(C9-C$5-(INT($M9/9)+(MOD($M9,9)&gt;=C$6)), 'Point System'!$A$4:$B$15, 2),"")</f>
@@ -1504,7 +1501,7 @@
       <c r="T10" s="2"/>
     </row>
     <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A11" s="67"/>
+      <c r="A11" s="58"/>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -1532,7 +1529,7 @@
       <c r="T11" s="1"/>
     </row>
     <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="68"/>
+      <c r="A12" s="59"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16" t="str">
         <f>IF(C11&gt;0, VLOOKUP(C11-C$5-(INT($M11/9)+(MOD($M11,9)&gt;=C$6)), 'Point System'!$A$4:$B$15, 2),"")</f>
@@ -1587,7 +1584,7 @@
       <c r="T12" s="1"/>
     </row>
     <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A13" s="67"/>
+      <c r="A13" s="58"/>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
@@ -1615,7 +1612,7 @@
       <c r="T13" s="1"/>
     </row>
     <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="68"/>
+      <c r="A14" s="59"/>
       <c r="B14" s="16"/>
       <c r="C14" s="16" t="str">
         <f>IF(C13&gt;0, VLOOKUP(C13-C$5-(INT($M13/9)+(MOD($M13,9)&gt;=C$6)), 'Point System'!$A$4:$B$15, 2),"")</f>
@@ -1670,7 +1667,7 @@
       <c r="T14" s="1"/>
     </row>
     <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A15" s="67"/>
+      <c r="A15" s="58"/>
       <c r="B15" s="12"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
@@ -1701,7 +1698,7 @@
       <c r="Z15" s="1"/>
     </row>
     <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="68"/>
+      <c r="A16" s="59"/>
       <c r="B16" s="16"/>
       <c r="C16" s="16" t="str">
         <f>IF(C15&gt;0, VLOOKUP(C15-C$5-(INT($M15/9)+(MOD($M15,9)&gt;=C$6)), 'Point System'!$A$4:$B$15, 2),"")</f>
@@ -1759,7 +1756,7 @@
       <c r="Z16" s="1"/>
     </row>
     <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A17" s="67"/>
+      <c r="A17" s="58"/>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -1790,7 +1787,7 @@
       <c r="Z17" s="1"/>
     </row>
     <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="68"/>
+      <c r="A18" s="59"/>
       <c r="B18" s="16"/>
       <c r="C18" s="16" t="str">
         <f>IF(C17&gt;0, VLOOKUP(C17-C$5-(INT($M17/9)+(MOD($M17,9)&gt;=C$6)), 'Point System'!$A$4:$B$15, 2),"")</f>
@@ -1848,7 +1845,7 @@
       <c r="Z18" s="1"/>
     </row>
     <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A19" s="67"/>
+      <c r="A19" s="58"/>
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -1875,7 +1872,7 @@
       <c r="T19" s="2"/>
     </row>
     <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="68"/>
+      <c r="A20" s="59"/>
       <c r="B20" s="16"/>
       <c r="C20" s="16" t="str">
         <f>IF(C19&gt;0, VLOOKUP(C19-C$5-(INT($M19/9)+(MOD($M19,9)&gt;=C$6)), 'Point System'!$A$4:$B$15, 2),"")</f>
@@ -1968,23 +1965,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="54" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
+      <c r="A1" s="68" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -1998,23 +1995,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="56" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
+      <c r="A2" s="70" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -2056,7 +2053,7 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="67" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="19" t="s">
@@ -3536,23 +3533,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="54" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
+      <c r="A1" s="68" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -3566,23 +3563,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="56" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
+      <c r="A2" s="70" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -3624,7 +3621,7 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="67" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="19" t="s">
@@ -4867,23 +4864,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="54" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
+      <c r="A1" s="68" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -4897,23 +4894,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="56" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
+      <c r="A2" s="70" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -4955,7 +4952,7 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="67" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="19" t="s">
@@ -6318,23 +6315,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="54" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
+      <c r="A1" s="68" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -6348,23 +6345,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="56" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
+      <c r="A2" s="70" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -6406,7 +6403,7 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="67" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="19" t="s">
@@ -8120,23 +8117,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="54" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
+      <c r="A1" s="68" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -8150,23 +8147,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="56" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
+      <c r="A2" s="70" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -8208,7 +8205,7 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="67" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="19" t="s">
@@ -9922,23 +9919,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="54" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
+      <c r="A1" s="68" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -9952,23 +9949,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="56" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
+      <c r="A2" s="70" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -10010,7 +10007,7 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="67" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="19" t="s">
@@ -11724,23 +11721,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="54" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
+      <c r="A1" s="68" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -11754,23 +11751,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="56" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
+      <c r="A2" s="70" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -11812,7 +11809,7 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="67" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="19" t="s">
@@ -13476,23 +13473,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="54" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
+      <c r="A1" s="68" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -13506,23 +13503,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="56" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
+      <c r="A2" s="70" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -13564,7 +13561,7 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="67" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="19" t="s">
@@ -15278,23 +15275,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="54" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
+      <c r="A1" s="68" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -15308,23 +15305,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="56" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
+      <c r="A2" s="70" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -15366,7 +15363,7 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="67" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="19" t="s">
@@ -18079,23 +18076,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="54" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
+      <c r="A1" s="68" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -18109,23 +18106,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="56" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
+      <c r="A2" s="70" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -18167,7 +18164,7 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="67" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="19" t="s">
@@ -19029,23 +19026,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="54" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
+      <c r="A1" s="68" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -19059,23 +19056,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="56" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
+      <c r="A2" s="70" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -19117,7 +19114,7 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="67" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="19" t="s">
@@ -19337,39 +19334,39 @@
         <v>25</v>
       </c>
       <c r="C8" s="16">
-        <f>IF(C7&gt;0, VLOOKUP(C7-C$5-(INT($M7/9)+(MOD($M7,9)&gt;=C$6)), '[1]Point System'!$A$4:$B$15, 2),"")</f>
+        <f>IF(C7&gt;0, VLOOKUP(C7-C$5-(INT($M7/9)+(MOD($M7,9)&gt;=C$6)), 'Point System'!$A$4:$B$15, 2),"")</f>
         <v>3</v>
       </c>
       <c r="D8" s="16">
-        <f>IF(D7&gt;0, VLOOKUP(D7-D$5-(INT($M7/9)+(MOD($M7,9)&gt;=D$6)), '[1]Point System'!$A$4:$B$15, 2),"")</f>
+        <f>IF(D7&gt;0, VLOOKUP(D7-D$5-(INT($M7/9)+(MOD($M7,9)&gt;=D$6)), 'Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
       <c r="E8" s="16">
-        <f>IF(E7&gt;0, VLOOKUP(E7-E$5-(INT($M7/9)+(MOD($M7,9)&gt;=E$6)), '[1]Point System'!$A$4:$B$15, 2),"")</f>
+        <f>IF(E7&gt;0, VLOOKUP(E7-E$5-(INT($M7/9)+(MOD($M7,9)&gt;=E$6)), 'Point System'!$A$4:$B$15, 2),"")</f>
         <v>4</v>
       </c>
       <c r="F8" s="16">
-        <f>IF(F7&gt;0, VLOOKUP(F7-F$5-(INT($M7/9)+(MOD($M7,9)&gt;=F$6)), '[1]Point System'!$A$4:$B$15, 2),"")</f>
+        <f>IF(F7&gt;0, VLOOKUP(F7-F$5-(INT($M7/9)+(MOD($M7,9)&gt;=F$6)), 'Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
       <c r="G8" s="16">
-        <f>IF(G7&gt;0, VLOOKUP(G7-G$5-(INT($M7/9)+(MOD($M7,9)&gt;=G$6)), '[1]Point System'!$A$4:$B$15, 2),"")</f>
+        <f>IF(G7&gt;0, VLOOKUP(G7-G$5-(INT($M7/9)+(MOD($M7,9)&gt;=G$6)), 'Point System'!$A$4:$B$15, 2),"")</f>
         <v>3</v>
       </c>
       <c r="H8" s="16">
-        <f>IF(H7&gt;0, VLOOKUP(H7-H$5-(INT($M7/9)+(MOD($M7,9)&gt;=H$6)), '[1]Point System'!$A$4:$B$15, 2),"")</f>
+        <f>IF(H7&gt;0, VLOOKUP(H7-H$5-(INT($M7/9)+(MOD($M7,9)&gt;=H$6)), 'Point System'!$A$4:$B$15, 2),"")</f>
         <v>2</v>
       </c>
       <c r="I8" s="16">
-        <f>IF(I7&gt;0, VLOOKUP(I7-I$5-(INT($M7/9)+(MOD($M7,9)&gt;=I$6)), '[1]Point System'!$A$4:$B$15, 2),"")</f>
+        <f>IF(I7&gt;0, VLOOKUP(I7-I$5-(INT($M7/9)+(MOD($M7,9)&gt;=I$6)), 'Point System'!$A$4:$B$15, 2),"")</f>
         <v>3</v>
       </c>
       <c r="J8" s="16">
-        <f>IF(J7&gt;0, VLOOKUP(J7-J$5-(INT($M7/9)+(MOD($M7,9)&gt;=J$6)), '[1]Point System'!$A$4:$B$15, 2),"")</f>
+        <f>IF(J7&gt;0, VLOOKUP(J7-J$5-(INT($M7/9)+(MOD($M7,9)&gt;=J$6)), 'Point System'!$A$4:$B$15, 2),"")</f>
         <v>3</v>
       </c>
       <c r="K8" s="16">
-        <f>IF(K7&gt;0, VLOOKUP(K7-K$5-(INT($M7/9)+(MOD($M7,9)&gt;=K$6)), '[1]Point System'!$A$4:$B$15, 2),"")</f>
+        <f>IF(K7&gt;0, VLOOKUP(K7-K$5-(INT($M7/9)+(MOD($M7,9)&gt;=K$6)), 'Point System'!$A$4:$B$15, 2),"")</f>
         <v>3</v>
       </c>
       <c r="L8" s="17">
@@ -20711,23 +20708,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="54" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
+      <c r="A1" s="68" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -20741,23 +20738,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="56" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
+      <c r="A2" s="70" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -20799,7 +20796,7 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="67" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="19" t="s">
@@ -21649,7 +21646,7 @@
   <dimension ref="A1:Z10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="73" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" style="64" customWidth="1"/>
     <col min="2" max="2" width="9.1640625" style="34" bestFit="1" customWidth="1"/>
     <col min="3" max="11" width="5" style="34" customWidth="1"/>
     <col min="12" max="12" width="5.1640625" style="34" bestFit="1" customWidth="1"/>
@@ -21661,23 +21658,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="17" x14ac:dyDescent="0.3">
-      <c r="A1" s="57" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
-      <c r="M1" s="58"/>
-      <c r="N1" s="58"/>
-      <c r="O1" s="58"/>
+      <c r="A1" s="71" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="72"/>
+      <c r="O1" s="72"/>
       <c r="P1" s="35"/>
       <c r="Q1" s="35"/>
       <c r="R1" s="35"/>
@@ -21691,23 +21688,23 @@
       <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="59" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="M2" s="58"/>
-      <c r="N2" s="58"/>
-      <c r="O2" s="58"/>
+      <c r="A2" s="73" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
+      <c r="N2" s="72"/>
+      <c r="O2" s="72"/>
       <c r="P2" s="35"/>
       <c r="Q2" s="35"/>
       <c r="R2" s="35"/>
@@ -21721,7 +21718,7 @@
       <c r="Z2" s="35"/>
     </row>
     <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="69"/>
+      <c r="A3" s="60"/>
       <c r="B3" s="35"/>
       <c r="C3" s="37"/>
       <c r="D3" s="37"/>
@@ -21749,7 +21746,7 @@
       <c r="Z3" s="35"/>
     </row>
     <row r="4" spans="1:26" ht="40" x14ac:dyDescent="0.2">
-      <c r="A4" s="70" t="s">
+      <c r="A4" s="61" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="39" t="s">
@@ -21807,7 +21804,7 @@
       <c r="Z4" s="36"/>
     </row>
     <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A5" s="71"/>
+      <c r="A5" s="62"/>
       <c r="B5" s="41" t="s">
         <v>10</v>
       </c>
@@ -21858,7 +21855,7 @@
       <c r="Z5" s="36"/>
     </row>
     <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="72"/>
+      <c r="A6" s="63"/>
       <c r="B6" s="44" t="s">
         <v>24</v>
       </c>
@@ -21906,7 +21903,7 @@
       <c r="Z6" s="36"/>
     </row>
     <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A7" s="74" t="s">
+      <c r="A7" s="65" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="47" t="s">
@@ -21964,7 +21961,7 @@
       <c r="Z7" s="35"/>
     </row>
     <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="75"/>
+      <c r="A8" s="66"/>
       <c r="B8" s="50" t="s">
         <v>25</v>
       </c>
@@ -22027,7 +22024,7 @@
       <c r="Z8" s="35"/>
     </row>
     <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A9" s="74" t="s">
+      <c r="A9" s="65" t="s">
         <v>29</v>
       </c>
       <c r="B9" s="47"/>
@@ -22083,7 +22080,7 @@
       <c r="Z9" s="35"/>
     </row>
     <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="75"/>
+      <c r="A10" s="66"/>
       <c r="B10" s="50"/>
       <c r="C10" s="16">
         <f>IF(C9&gt;0, VLOOKUP(C9-C$5-(INT($M9/9)+(MOD($M9,9)&gt;=C$6)), 'Point System'!$A$4:$B$15, 2),"")</f>
@@ -22173,23 +22170,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="54" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
+      <c r="A1" s="68" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -22203,23 +22200,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="56" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
+      <c r="A2" s="70" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -22261,7 +22258,7 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="67" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="19" t="s">
@@ -23237,23 +23234,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="54" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
+      <c r="A1" s="68" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -23267,23 +23264,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="56" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
+      <c r="A2" s="70" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -23325,7 +23322,7 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="67" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="19" t="s">
@@ -24793,23 +24790,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="54" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
+      <c r="A1" s="68" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -24823,23 +24820,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="56" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
+      <c r="A2" s="70" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -24881,7 +24878,7 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="67" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="19" t="s">

--- a/public/results/2025/2025 Weekly Stats - Week 16.xlsx
+++ b/public/results/2025/2025 Weekly Stats - Week 16.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mthutter/CODE/golf-league-site/public/results/2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3181B8A7-654A-CA4E-BB38-B19FF68D8EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76A66946-756E-684D-B434-9E4DCC9E386E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1300" yWindow="500" windowWidth="28100" windowHeight="19840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1300" yWindow="500" windowWidth="14320" windowHeight="19840" firstSheet="11" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="14" r:id="rId1"/>

--- a/public/results/2025/2025 Weekly Stats - Week 16.xlsx
+++ b/public/results/2025/2025 Weekly Stats - Week 16.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr updateLinks="always"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mthutter/CODE/golf-league-site/public/results/2025/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\CODE\golf-league-site\public\results\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76A66946-756E-684D-B434-9E4DCC9E386E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{298D676A-3028-499F-83AE-463262407E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1300" yWindow="500" windowWidth="14320" windowHeight="19840" firstSheet="11" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="930" yWindow="45" windowWidth="19470" windowHeight="10755" firstSheet="9" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="14" r:id="rId1"/>
@@ -1058,25 +1058,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75685173-5684-4D7E-8458-1B841D06EDCF}">
   <dimension ref="A1:Z21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23" style="28" customWidth="1"/>
     <col min="2" max="2" width="15" style="2" customWidth="1"/>
     <col min="3" max="11" width="5" style="2" customWidth="1"/>
-    <col min="12" max="12" width="5.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.1640625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="7.5" style="2" customWidth="1"/>
-    <col min="15" max="15" width="17.1640625" style="2" customWidth="1"/>
-    <col min="16" max="16" width="8.6640625" style="2" customWidth="1"/>
-    <col min="17" max="17" width="15.1640625" style="2" customWidth="1"/>
-    <col min="18" max="18" width="13.6640625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="8.6640625" style="2" customWidth="1"/>
-    <col min="20" max="20" width="8.6640625" style="31" customWidth="1"/>
-    <col min="21" max="26" width="8.6640625" style="2" customWidth="1"/>
-    <col min="27" max="16384" width="14.1640625" style="2"/>
+    <col min="12" max="12" width="5.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.140625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="7.42578125" style="2" customWidth="1"/>
+    <col min="15" max="15" width="17.140625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="15.140625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="13.7109375" style="2" customWidth="1"/>
+    <col min="19" max="19" width="8.7109375" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.7109375" style="31" customWidth="1"/>
+    <col min="21" max="26" width="8.7109375" style="2" customWidth="1"/>
+    <col min="27" max="16384" width="14.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="68" t="s">
         <v>2</v>
       </c>
@@ -1106,7 +1106,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="70" t="s">
         <v>3</v>
       </c>
@@ -1136,7 +1136,7 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
-    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8"/>
       <c r="B3" s="1"/>
       <c r="C3" s="4"/>
@@ -1164,7 +1164,7 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="55" t="s">
         <v>4</v>
       </c>
@@ -1222,7 +1222,7 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A5" s="56"/>
       <c r="B5" s="6" t="s">
         <v>10</v>
@@ -1273,7 +1273,7 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
     </row>
-    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="57"/>
       <c r="B6" s="24" t="s">
         <v>24</v>
@@ -1321,7 +1321,7 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A7" s="58"/>
       <c r="B7" s="12" t="s">
         <v>23</v>
@@ -1357,7 +1357,7 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="59"/>
       <c r="B8" s="16" t="s">
         <v>25</v>
@@ -1419,7 +1419,7 @@
       <c r="X8" s="1"/>
       <c r="Z8" s="33"/>
     </row>
-    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A9" s="58"/>
       <c r="B9" s="12"/>
       <c r="C9" s="12"/>
@@ -1446,7 +1446,7 @@
       <c r="R9" s="29"/>
       <c r="T9" s="2"/>
     </row>
-    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="59"/>
       <c r="B10" s="16"/>
       <c r="C10" s="16" t="str">
@@ -1500,7 +1500,7 @@
       <c r="R10" s="29"/>
       <c r="T10" s="2"/>
     </row>
-    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A11" s="58"/>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
@@ -1528,7 +1528,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="59"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16" t="str">
@@ -1583,7 +1583,7 @@
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A13" s="58"/>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
@@ -1611,7 +1611,7 @@
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="59"/>
       <c r="B14" s="16"/>
       <c r="C14" s="16" t="str">
@@ -1666,7 +1666,7 @@
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A15" s="58"/>
       <c r="B15" s="12"/>
       <c r="C15" s="12"/>
@@ -1697,7 +1697,7 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="59"/>
       <c r="B16" s="16"/>
       <c r="C16" s="16" t="str">
@@ -1755,7 +1755,7 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A17" s="58"/>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
@@ -1786,7 +1786,7 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="59"/>
       <c r="B18" s="16"/>
       <c r="C18" s="16" t="str">
@@ -1844,7 +1844,7 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A19" s="58"/>
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
@@ -1871,7 +1871,7 @@
       <c r="R19" s="29"/>
       <c r="T19" s="2"/>
     </row>
-    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="59"/>
       <c r="B20" s="16"/>
       <c r="C20" s="16" t="str">
@@ -1925,7 +1925,7 @@
       <c r="R20" s="29"/>
       <c r="T20" s="2"/>
     </row>
-    <row r="21" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E21" s="28"/>
       <c r="G21" s="28"/>
       <c r="H21" s="28"/>
@@ -1951,20 +1951,20 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BB9E8EB-7163-3848-BDED-B51E8101CF15}">
   <dimension ref="A1:Z28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
     <col min="3" max="11" width="5" style="2" customWidth="1"/>
-    <col min="12" max="12" width="5.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17" style="2" customWidth="1"/>
-    <col min="16" max="26" width="8.6640625" style="2" customWidth="1"/>
-    <col min="27" max="16384" width="14.1640625" style="2"/>
+    <col min="16" max="26" width="8.7109375" style="2" customWidth="1"/>
+    <col min="27" max="16384" width="14.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="68" t="s">
         <v>2</v>
       </c>
@@ -1994,7 +1994,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="70" t="s">
         <v>3</v>
       </c>
@@ -2024,7 +2024,7 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
-    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
       <c r="B3" s="1"/>
       <c r="C3" s="4"/>
@@ -2052,7 +2052,7 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A4" s="67" t="s">
         <v>4</v>
       </c>
@@ -2110,7 +2110,7 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A5" s="21"/>
       <c r="B5" s="6" t="s">
         <v>10</v>
@@ -2161,7 +2161,7 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
     </row>
-    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="23"/>
       <c r="B6" s="24" t="s">
         <v>24</v>
@@ -2209,7 +2209,7 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>34</v>
       </c>
@@ -2240,7 +2240,7 @@
       <c r="J7" s="12">
         <v>4</v>
       </c>
-      <c r="K7" s="12">
+      <c r="K7" s="53">
         <v>4</v>
       </c>
       <c r="L7" s="13">
@@ -2267,7 +2267,7 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15"/>
       <c r="B8" s="16" t="s">
         <v>25</v>
@@ -2330,7 +2330,7 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>35</v>
       </c>
@@ -2386,7 +2386,7 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
     </row>
-    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15"/>
       <c r="B10" s="16"/>
       <c r="C10" s="16">
@@ -2447,7 +2447,7 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>27</v>
       </c>
@@ -2503,7 +2503,7 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16">
@@ -2564,7 +2564,7 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>21</v>
       </c>
@@ -2620,7 +2620,7 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15"/>
       <c r="B14" s="16"/>
       <c r="C14" s="16">
@@ -2681,7 +2681,7 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>16</v>
       </c>
@@ -2737,7 +2737,7 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15"/>
       <c r="B16" s="16"/>
       <c r="C16" s="16">
@@ -2798,7 +2798,7 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>12</v>
       </c>
@@ -2854,7 +2854,7 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15"/>
       <c r="B18" s="16"/>
       <c r="C18" s="16">
@@ -2915,7 +2915,7 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>14</v>
       </c>
@@ -2971,7 +2971,7 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15"/>
       <c r="B20" s="16"/>
       <c r="C20" s="16">
@@ -3032,7 +3032,7 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>15</v>
       </c>
@@ -3088,7 +3088,7 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15"/>
       <c r="B22" s="16"/>
       <c r="C22" s="16">
@@ -3149,7 +3149,7 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>33</v>
       </c>
@@ -3205,7 +3205,7 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15"/>
       <c r="B24" s="16"/>
       <c r="C24" s="16">
@@ -3266,7 +3266,7 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>29</v>
       </c>
@@ -3322,7 +3322,7 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15"/>
       <c r="B26" s="16"/>
       <c r="C26" s="16">
@@ -3383,7 +3383,7 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>36</v>
       </c>
@@ -3439,7 +3439,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="15"/>
       <c r="B28" s="16"/>
       <c r="C28" s="16">
@@ -3519,20 +3519,20 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3C3F21F-86A7-B948-B341-41C284BC644B}">
   <dimension ref="A1:Z24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="11" width="5" style="2" customWidth="1"/>
-    <col min="12" max="12" width="5.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17" style="2" customWidth="1"/>
-    <col min="16" max="26" width="8.6640625" style="2" customWidth="1"/>
-    <col min="27" max="16384" width="14.1640625" style="2"/>
+    <col min="16" max="26" width="8.7109375" style="2" customWidth="1"/>
+    <col min="27" max="16384" width="14.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="68" t="s">
         <v>2</v>
       </c>
@@ -3562,7 +3562,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="70" t="s">
         <v>3</v>
       </c>
@@ -3592,7 +3592,7 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
-    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
       <c r="B3" s="1"/>
       <c r="C3" s="4"/>
@@ -3620,7 +3620,7 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A4" s="67" t="s">
         <v>4</v>
       </c>
@@ -3678,7 +3678,7 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A5" s="21"/>
       <c r="B5" s="6" t="s">
         <v>10</v>
@@ -3729,7 +3729,7 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
     </row>
-    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="23"/>
       <c r="B6" s="24" t="s">
         <v>24</v>
@@ -3777,7 +3777,7 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -3835,7 +3835,7 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15"/>
       <c r="B8" s="16" t="s">
         <v>25</v>
@@ -3898,7 +3898,7 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>13</v>
       </c>
@@ -3954,7 +3954,7 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
     </row>
-    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15"/>
       <c r="B10" s="16"/>
       <c r="C10" s="16">
@@ -4015,7 +4015,7 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>26</v>
       </c>
@@ -4071,7 +4071,7 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16">
@@ -4132,7 +4132,7 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>14</v>
       </c>
@@ -4188,7 +4188,7 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15"/>
       <c r="B14" s="16"/>
       <c r="C14" s="16">
@@ -4249,7 +4249,7 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>15</v>
       </c>
@@ -4305,7 +4305,7 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15"/>
       <c r="B16" s="16"/>
       <c r="C16" s="16">
@@ -4366,7 +4366,7 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>33</v>
       </c>
@@ -4422,7 +4422,7 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15"/>
       <c r="B18" s="16"/>
       <c r="C18" s="16">
@@ -4483,7 +4483,7 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>35</v>
       </c>
@@ -4539,7 +4539,7 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15"/>
       <c r="B20" s="16"/>
       <c r="C20" s="16">
@@ -4600,7 +4600,7 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>27</v>
       </c>
@@ -4656,7 +4656,7 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15"/>
       <c r="B22" s="16"/>
       <c r="C22" s="16">
@@ -4717,7 +4717,7 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>12</v>
       </c>
@@ -4773,7 +4773,7 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15"/>
       <c r="B24" s="16"/>
       <c r="C24" s="16">
@@ -4850,20 +4850,20 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E8FA2D2-E7CB-EF49-BC2B-5A3BAC2AF723}">
   <dimension ref="A1:Z26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="11" width="5" style="2" customWidth="1"/>
-    <col min="12" max="12" width="5.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17" style="2" customWidth="1"/>
-    <col min="16" max="26" width="8.6640625" style="2" customWidth="1"/>
-    <col min="27" max="16384" width="14.1640625" style="2"/>
+    <col min="16" max="26" width="8.7109375" style="2" customWidth="1"/>
+    <col min="27" max="16384" width="14.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="68" t="s">
         <v>2</v>
       </c>
@@ -4893,7 +4893,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="70" t="s">
         <v>3</v>
       </c>
@@ -4923,7 +4923,7 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
-    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
       <c r="B3" s="1"/>
       <c r="C3" s="4"/>
@@ -4951,7 +4951,7 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A4" s="67" t="s">
         <v>4</v>
       </c>
@@ -5009,7 +5009,7 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A5" s="21"/>
       <c r="B5" s="6" t="s">
         <v>10</v>
@@ -5060,7 +5060,7 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
     </row>
-    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="23"/>
       <c r="B6" s="24" t="s">
         <v>24</v>
@@ -5108,7 +5108,7 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>14</v>
       </c>
@@ -5166,7 +5166,7 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15"/>
       <c r="B8" s="16" t="s">
         <v>25</v>
@@ -5229,7 +5229,7 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>26</v>
       </c>
@@ -5285,7 +5285,7 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
     </row>
-    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15"/>
       <c r="B10" s="16"/>
       <c r="C10" s="16">
@@ -5346,7 +5346,7 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
@@ -5402,7 +5402,7 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16">
@@ -5463,7 +5463,7 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>36</v>
       </c>
@@ -5519,7 +5519,7 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15"/>
       <c r="B14" s="16"/>
       <c r="C14" s="16">
@@ -5580,7 +5580,7 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>13</v>
       </c>
@@ -5636,7 +5636,7 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15"/>
       <c r="B16" s="16"/>
       <c r="C16" s="16">
@@ -5697,7 +5697,7 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>34</v>
       </c>
@@ -5717,7 +5717,7 @@
       <c r="G17" s="12">
         <v>4</v>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="53">
         <v>3</v>
       </c>
       <c r="I17" s="12">
@@ -5753,7 +5753,7 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15"/>
       <c r="B18" s="16"/>
       <c r="C18" s="16">
@@ -5814,7 +5814,7 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>12</v>
       </c>
@@ -5870,7 +5870,7 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15"/>
       <c r="B20" s="16"/>
       <c r="C20" s="16">
@@ -5931,7 +5931,7 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>33</v>
       </c>
@@ -5987,7 +5987,7 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15"/>
       <c r="B22" s="16"/>
       <c r="C22" s="16">
@@ -6048,7 +6048,7 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>21</v>
       </c>
@@ -6104,7 +6104,7 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15"/>
       <c r="B24" s="16"/>
       <c r="C24" s="16">
@@ -6165,7 +6165,7 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>16</v>
       </c>
@@ -6221,7 +6221,7 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15"/>
       <c r="B26" s="16"/>
       <c r="C26" s="16">
@@ -6301,20 +6301,20 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{590B39FE-5332-4F44-A7CA-DA96F833A67E}">
   <dimension ref="A1:Z32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="11" width="5" style="2" customWidth="1"/>
-    <col min="12" max="12" width="5.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17" style="2" customWidth="1"/>
-    <col min="16" max="26" width="8.6640625" style="2" customWidth="1"/>
-    <col min="27" max="16384" width="14.1640625" style="2"/>
+    <col min="16" max="26" width="8.7109375" style="2" customWidth="1"/>
+    <col min="27" max="16384" width="14.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="68" t="s">
         <v>2</v>
       </c>
@@ -6344,7 +6344,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="70" t="s">
         <v>3</v>
       </c>
@@ -6374,7 +6374,7 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
-    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
       <c r="B3" s="1"/>
       <c r="C3" s="4"/>
@@ -6402,7 +6402,7 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A4" s="67" t="s">
         <v>4</v>
       </c>
@@ -6460,7 +6460,7 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A5" s="21"/>
       <c r="B5" s="6" t="s">
         <v>10</v>
@@ -6511,7 +6511,7 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
     </row>
-    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="23"/>
       <c r="B6" s="24" t="s">
         <v>24</v>
@@ -6559,7 +6559,7 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>11</v>
       </c>
@@ -6617,7 +6617,7 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15"/>
       <c r="B8" s="16" t="s">
         <v>25</v>
@@ -6680,7 +6680,7 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>31</v>
       </c>
@@ -6736,7 +6736,7 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
     </row>
-    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15"/>
       <c r="B10" s="16"/>
       <c r="C10" s="16">
@@ -6797,7 +6797,7 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>13</v>
       </c>
@@ -6853,7 +6853,7 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16">
@@ -6914,7 +6914,7 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
@@ -6970,7 +6970,7 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15"/>
       <c r="B14" s="16"/>
       <c r="C14" s="16">
@@ -7031,7 +7031,7 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>34</v>
       </c>
@@ -7087,7 +7087,7 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15"/>
       <c r="B16" s="16"/>
       <c r="C16" s="16">
@@ -7148,7 +7148,7 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>32</v>
       </c>
@@ -7204,7 +7204,7 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15"/>
       <c r="B18" s="16"/>
       <c r="C18" s="16">
@@ -7265,7 +7265,7 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>36</v>
       </c>
@@ -7321,7 +7321,7 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15"/>
       <c r="B20" s="16"/>
       <c r="C20" s="16">
@@ -7382,7 +7382,7 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>33</v>
       </c>
@@ -7438,7 +7438,7 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15"/>
       <c r="B22" s="16"/>
       <c r="C22" s="16">
@@ -7499,7 +7499,7 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>14</v>
       </c>
@@ -7555,7 +7555,7 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15"/>
       <c r="B24" s="16"/>
       <c r="C24" s="16">
@@ -7616,7 +7616,7 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>35</v>
       </c>
@@ -7672,7 +7672,7 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15"/>
       <c r="B26" s="16"/>
       <c r="C26" s="16">
@@ -7733,7 +7733,7 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>28</v>
       </c>
@@ -7789,7 +7789,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="15"/>
       <c r="B28" s="16"/>
       <c r="C28" s="16">
@@ -7850,7 +7850,7 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>16</v>
       </c>
@@ -7906,7 +7906,7 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="15"/>
       <c r="B30" s="16"/>
       <c r="C30" s="16">
@@ -7967,7 +7967,7 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>12</v>
       </c>
@@ -8023,7 +8023,7 @@
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
     </row>
-    <row r="32" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="15"/>
       <c r="B32" s="16"/>
       <c r="C32" s="16">
@@ -8103,20 +8103,20 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1BBB3E6-C6EE-6A4F-8D6A-361AF94230C4}">
   <dimension ref="A1:Z32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="11" width="5" style="2" customWidth="1"/>
-    <col min="12" max="12" width="5.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17" style="2" customWidth="1"/>
-    <col min="16" max="26" width="8.6640625" style="2" customWidth="1"/>
-    <col min="27" max="16384" width="14.1640625" style="2"/>
+    <col min="16" max="26" width="8.7109375" style="2" customWidth="1"/>
+    <col min="27" max="16384" width="14.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="68" t="s">
         <v>2</v>
       </c>
@@ -8146,7 +8146,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="70" t="s">
         <v>3</v>
       </c>
@@ -8176,7 +8176,7 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
-    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
       <c r="B3" s="1"/>
       <c r="C3" s="4"/>
@@ -8204,7 +8204,7 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A4" s="67" t="s">
         <v>4</v>
       </c>
@@ -8262,7 +8262,7 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A5" s="21"/>
       <c r="B5" s="6" t="s">
         <v>10</v>
@@ -8313,7 +8313,7 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
     </row>
-    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="23"/>
       <c r="B6" s="24" t="s">
         <v>24</v>
@@ -8361,7 +8361,7 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>13</v>
       </c>
@@ -8419,7 +8419,7 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15"/>
       <c r="B8" s="16" t="s">
         <v>25</v>
@@ -8482,7 +8482,7 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>32</v>
       </c>
@@ -8538,7 +8538,7 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
     </row>
-    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15"/>
       <c r="B10" s="16"/>
       <c r="C10" s="16">
@@ -8599,7 +8599,7 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>31</v>
       </c>
@@ -8655,7 +8655,7 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16">
@@ -8716,7 +8716,7 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>27</v>
       </c>
@@ -8772,7 +8772,7 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15"/>
       <c r="B14" s="16"/>
       <c r="C14" s="16">
@@ -8833,7 +8833,7 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>14</v>
       </c>
@@ -8889,7 +8889,7 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15"/>
       <c r="B16" s="16"/>
       <c r="C16" s="16">
@@ -8950,7 +8950,7 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>15</v>
       </c>
@@ -9006,7 +9006,7 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15"/>
       <c r="B18" s="16"/>
       <c r="C18" s="16">
@@ -9067,7 +9067,7 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>16</v>
       </c>
@@ -9123,7 +9123,7 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15"/>
       <c r="B20" s="16"/>
       <c r="C20" s="16">
@@ -9184,7 +9184,7 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>34</v>
       </c>
@@ -9240,7 +9240,7 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15"/>
       <c r="B22" s="16"/>
       <c r="C22" s="16">
@@ -9301,7 +9301,7 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>11</v>
       </c>
@@ -9357,7 +9357,7 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15"/>
       <c r="B24" s="16"/>
       <c r="C24" s="16">
@@ -9418,7 +9418,7 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>26</v>
       </c>
@@ -9474,7 +9474,7 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15"/>
       <c r="B26" s="16"/>
       <c r="C26" s="16">
@@ -9535,7 +9535,7 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>33</v>
       </c>
@@ -9591,7 +9591,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="15"/>
       <c r="B28" s="16"/>
       <c r="C28" s="16">
@@ -9652,7 +9652,7 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>35</v>
       </c>
@@ -9708,7 +9708,7 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="15"/>
       <c r="B30" s="16"/>
       <c r="C30" s="16">
@@ -9769,7 +9769,7 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>12</v>
       </c>
@@ -9825,7 +9825,7 @@
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
     </row>
-    <row r="32" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="15"/>
       <c r="B32" s="16"/>
       <c r="C32" s="16">
@@ -9905,20 +9905,20 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85CFFFF4-7DCE-AE4F-A3FB-E8DE4BB08B1A}">
   <dimension ref="A1:Z32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="11" width="5" style="2" customWidth="1"/>
-    <col min="12" max="12" width="5.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17" style="2" customWidth="1"/>
-    <col min="16" max="26" width="8.6640625" style="2" customWidth="1"/>
-    <col min="27" max="16384" width="14.1640625" style="2"/>
+    <col min="16" max="26" width="8.7109375" style="2" customWidth="1"/>
+    <col min="27" max="16384" width="14.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="68" t="s">
         <v>2</v>
       </c>
@@ -9948,7 +9948,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="70" t="s">
         <v>3</v>
       </c>
@@ -9978,7 +9978,7 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
-    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
       <c r="B3" s="1"/>
       <c r="C3" s="4"/>
@@ -10006,7 +10006,7 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A4" s="67" t="s">
         <v>4</v>
       </c>
@@ -10064,7 +10064,7 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A5" s="21"/>
       <c r="B5" s="6" t="s">
         <v>10</v>
@@ -10115,7 +10115,7 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
     </row>
-    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="23"/>
       <c r="B6" s="24" t="s">
         <v>24</v>
@@ -10163,7 +10163,7 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -10221,7 +10221,7 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15"/>
       <c r="B8" s="16" t="s">
         <v>25</v>
@@ -10284,7 +10284,7 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>26</v>
       </c>
@@ -10340,7 +10340,7 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
     </row>
-    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15"/>
       <c r="B10" s="16"/>
       <c r="C10" s="16">
@@ -10401,7 +10401,7 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>13</v>
       </c>
@@ -10457,7 +10457,7 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16">
@@ -10518,7 +10518,7 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>35</v>
       </c>
@@ -10574,7 +10574,7 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15"/>
       <c r="B14" s="16"/>
       <c r="C14" s="16">
@@ -10635,7 +10635,7 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>34</v>
       </c>
@@ -10691,7 +10691,7 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15"/>
       <c r="B16" s="16"/>
       <c r="C16" s="16">
@@ -10752,7 +10752,7 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>15</v>
       </c>
@@ -10808,7 +10808,7 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15"/>
       <c r="B18" s="16"/>
       <c r="C18" s="16">
@@ -10869,7 +10869,7 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>36</v>
       </c>
@@ -10925,7 +10925,7 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15"/>
       <c r="B20" s="16"/>
       <c r="C20" s="16">
@@ -10986,7 +10986,7 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>14</v>
       </c>
@@ -11042,7 +11042,7 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15"/>
       <c r="B22" s="16"/>
       <c r="C22" s="16">
@@ -11103,7 +11103,7 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>32</v>
       </c>
@@ -11159,7 +11159,7 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15"/>
       <c r="B24" s="16"/>
       <c r="C24" s="16">
@@ -11220,7 +11220,7 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>28</v>
       </c>
@@ -11276,7 +11276,7 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15"/>
       <c r="B26" s="16"/>
       <c r="C26" s="16">
@@ -11337,7 +11337,7 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>33</v>
       </c>
@@ -11393,7 +11393,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="15"/>
       <c r="B28" s="16"/>
       <c r="C28" s="16">
@@ -11454,7 +11454,7 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>11</v>
       </c>
@@ -11510,7 +11510,7 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="15"/>
       <c r="B30" s="16"/>
       <c r="C30" s="16">
@@ -11571,7 +11571,7 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>12</v>
       </c>
@@ -11627,7 +11627,7 @@
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
     </row>
-    <row r="32" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="15"/>
       <c r="B32" s="16"/>
       <c r="C32" s="16">
@@ -11707,20 +11707,20 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40217437-D440-6142-8416-6B7D6376EFBB}">
   <dimension ref="A1:Z32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="11" width="5" style="2" customWidth="1"/>
-    <col min="12" max="12" width="5.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17" style="2" customWidth="1"/>
-    <col min="16" max="26" width="8.6640625" style="2" customWidth="1"/>
-    <col min="27" max="16384" width="14.1640625" style="2"/>
+    <col min="16" max="26" width="8.7109375" style="2" customWidth="1"/>
+    <col min="27" max="16384" width="14.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="68" t="s">
         <v>2</v>
       </c>
@@ -11750,7 +11750,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="70" t="s">
         <v>3</v>
       </c>
@@ -11780,7 +11780,7 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
-    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
       <c r="B3" s="1"/>
       <c r="C3" s="4"/>
@@ -11808,7 +11808,7 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A4" s="67" t="s">
         <v>4</v>
       </c>
@@ -11866,7 +11866,7 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A5" s="21"/>
       <c r="B5" s="6" t="s">
         <v>10</v>
@@ -11917,7 +11917,7 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
     </row>
-    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="23"/>
       <c r="B6" s="24" t="s">
         <v>24</v>
@@ -11965,7 +11965,7 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>34</v>
       </c>
@@ -12023,7 +12023,7 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15"/>
       <c r="B8" s="16" t="s">
         <v>25</v>
@@ -12086,7 +12086,7 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>32</v>
       </c>
@@ -12142,7 +12142,7 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
     </row>
-    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15"/>
       <c r="B10" s="16"/>
       <c r="C10" s="16">
@@ -12203,7 +12203,7 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>14</v>
       </c>
@@ -12259,7 +12259,7 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16">
@@ -12320,7 +12320,7 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>13</v>
       </c>
@@ -12376,7 +12376,7 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15"/>
       <c r="B14" s="16"/>
       <c r="C14" s="16">
@@ -12437,7 +12437,7 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>11</v>
       </c>
@@ -12493,7 +12493,7 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15"/>
       <c r="B16" s="16"/>
       <c r="C16" s="16">
@@ -12554,7 +12554,7 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>26</v>
       </c>
@@ -12610,7 +12610,7 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15"/>
       <c r="B18" s="16"/>
       <c r="C18" s="16">
@@ -12671,7 +12671,7 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -12727,7 +12727,7 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15"/>
       <c r="B20" s="16"/>
       <c r="C20" s="16">
@@ -12788,7 +12788,7 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>33</v>
       </c>
@@ -12844,7 +12844,7 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15"/>
       <c r="B22" s="16"/>
       <c r="C22" s="16">
@@ -12905,7 +12905,7 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>12</v>
       </c>
@@ -12961,7 +12961,7 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15"/>
       <c r="B24" s="16"/>
       <c r="C24" s="16">
@@ -13022,7 +13022,7 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>31</v>
       </c>
@@ -13078,7 +13078,7 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15"/>
       <c r="B26" s="16"/>
       <c r="C26" s="16">
@@ -13139,7 +13139,7 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>27</v>
       </c>
@@ -13195,7 +13195,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="15"/>
       <c r="B28" s="16"/>
       <c r="C28" s="16">
@@ -13256,7 +13256,7 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -13287,7 +13287,7 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="15"/>
       <c r="B30" s="16"/>
       <c r="C30" s="16" t="str">
@@ -13348,7 +13348,7 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="12"/>
       <c r="C31" s="12"/>
@@ -13379,7 +13379,7 @@
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
     </row>
-    <row r="32" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="15"/>
       <c r="B32" s="16"/>
       <c r="C32" s="16" t="str">
@@ -13459,20 +13459,20 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FAE2511-7E79-FD46-B471-0CAEE99F4672}">
   <dimension ref="A1:Z32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="11" width="5" style="2" customWidth="1"/>
-    <col min="12" max="12" width="5.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17" style="2" customWidth="1"/>
-    <col min="16" max="26" width="8.6640625" style="2" customWidth="1"/>
-    <col min="27" max="16384" width="14.1640625" style="2"/>
+    <col min="16" max="26" width="8.7109375" style="2" customWidth="1"/>
+    <col min="27" max="16384" width="14.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="68" t="s">
         <v>2</v>
       </c>
@@ -13502,7 +13502,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="70" t="s">
         <v>3</v>
       </c>
@@ -13532,7 +13532,7 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
-    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
       <c r="B3" s="1"/>
       <c r="C3" s="4"/>
@@ -13560,7 +13560,7 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A4" s="67" t="s">
         <v>4</v>
       </c>
@@ -13618,7 +13618,7 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A5" s="21"/>
       <c r="B5" s="6" t="s">
         <v>10</v>
@@ -13669,7 +13669,7 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
     </row>
-    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="23"/>
       <c r="B6" s="24" t="s">
         <v>24</v>
@@ -13717,7 +13717,7 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>26</v>
       </c>
@@ -13775,7 +13775,7 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15"/>
       <c r="B8" s="16" t="s">
         <v>25</v>
@@ -13838,7 +13838,7 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>27</v>
       </c>
@@ -13894,7 +13894,7 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
     </row>
-    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15"/>
       <c r="B10" s="16"/>
       <c r="C10" s="16">
@@ -13955,7 +13955,7 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>31</v>
       </c>
@@ -14011,7 +14011,7 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16">
@@ -14072,7 +14072,7 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>36</v>
       </c>
@@ -14128,7 +14128,7 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15"/>
       <c r="B14" s="16"/>
       <c r="C14" s="16">
@@ -14189,7 +14189,7 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>35</v>
       </c>
@@ -14245,7 +14245,7 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15"/>
       <c r="B16" s="16"/>
       <c r="C16" s="16">
@@ -14306,7 +14306,7 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>12</v>
       </c>
@@ -14362,7 +14362,7 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15"/>
       <c r="B18" s="16"/>
       <c r="C18" s="16">
@@ -14423,7 +14423,7 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>11</v>
       </c>
@@ -14479,7 +14479,7 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15"/>
       <c r="B20" s="16"/>
       <c r="C20" s="16">
@@ -14540,7 +14540,7 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>13</v>
       </c>
@@ -14596,7 +14596,7 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15"/>
       <c r="B22" s="16"/>
       <c r="C22" s="16">
@@ -14657,7 +14657,7 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>29</v>
       </c>
@@ -14713,7 +14713,7 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15"/>
       <c r="B24" s="16"/>
       <c r="C24" s="16">
@@ -14774,7 +14774,7 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>33</v>
       </c>
@@ -14830,7 +14830,7 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15"/>
       <c r="B26" s="16"/>
       <c r="C26" s="16">
@@ -14891,7 +14891,7 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>14</v>
       </c>
@@ -14947,7 +14947,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="15"/>
       <c r="B28" s="16"/>
       <c r="C28" s="16">
@@ -15008,7 +15008,7 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>34</v>
       </c>
@@ -15064,7 +15064,7 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="15"/>
       <c r="B30" s="16"/>
       <c r="C30" s="16">
@@ -15125,7 +15125,7 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>32</v>
       </c>
@@ -15181,7 +15181,7 @@
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
     </row>
-    <row r="32" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="15"/>
       <c r="B32" s="16"/>
       <c r="C32" s="16">
@@ -15261,20 +15261,20 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8EBAD32-82C5-E647-BBDC-0257FB18DB0F}">
   <dimension ref="A1:Z30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="11" width="5" style="2" customWidth="1"/>
-    <col min="12" max="12" width="5.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17" style="2" customWidth="1"/>
-    <col min="16" max="26" width="8.6640625" style="2" customWidth="1"/>
-    <col min="27" max="16384" width="14.1640625" style="2"/>
+    <col min="16" max="26" width="8.7109375" style="2" customWidth="1"/>
+    <col min="27" max="16384" width="14.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="68" t="s">
         <v>2</v>
       </c>
@@ -15304,7 +15304,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="70" t="s">
         <v>3</v>
       </c>
@@ -15334,7 +15334,7 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
-    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
       <c r="B3" s="1"/>
       <c r="C3" s="4"/>
@@ -15362,7 +15362,7 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A4" s="67" t="s">
         <v>4</v>
       </c>
@@ -15420,7 +15420,7 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A5" s="21"/>
       <c r="B5" s="6" t="s">
         <v>10</v>
@@ -15471,7 +15471,7 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
     </row>
-    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="23"/>
       <c r="B6" s="24" t="s">
         <v>24</v>
@@ -15519,7 +15519,7 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -15577,7 +15577,7 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15"/>
       <c r="B8" s="16" t="s">
         <v>25</v>
@@ -15640,7 +15640,7 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>35</v>
       </c>
@@ -15696,7 +15696,7 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
     </row>
-    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15"/>
       <c r="B10" s="16"/>
       <c r="C10" s="16">
@@ -15757,7 +15757,7 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>26</v>
       </c>
@@ -15813,7 +15813,7 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16">
@@ -15874,7 +15874,7 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>13</v>
       </c>
@@ -15930,7 +15930,7 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15"/>
       <c r="B14" s="16"/>
       <c r="C14" s="16">
@@ -15991,7 +15991,7 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>33</v>
       </c>
@@ -16047,7 +16047,7 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15"/>
       <c r="B16" s="16"/>
       <c r="C16" s="16">
@@ -16108,7 +16108,7 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>11</v>
       </c>
@@ -16164,7 +16164,7 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15"/>
       <c r="B18" s="16"/>
       <c r="C18" s="16">
@@ -16225,7 +16225,7 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -16281,7 +16281,7 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15"/>
       <c r="B20" s="16"/>
       <c r="C20" s="16">
@@ -16342,7 +16342,7 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>34</v>
       </c>
@@ -16398,7 +16398,7 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15"/>
       <c r="B22" s="16"/>
       <c r="C22" s="16">
@@ -16459,7 +16459,7 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>32</v>
       </c>
@@ -16515,7 +16515,7 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15"/>
       <c r="B24" s="16"/>
       <c r="C24" s="16">
@@ -16576,7 +16576,7 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>14</v>
       </c>
@@ -16632,7 +16632,7 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15"/>
       <c r="B26" s="16"/>
       <c r="C26" s="16">
@@ -16693,7 +16693,7 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>16</v>
       </c>
@@ -16749,7 +16749,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="15"/>
       <c r="B28" s="16"/>
       <c r="C28" s="16">
@@ -16810,7 +16810,7 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>12</v>
       </c>
@@ -16866,7 +16866,7 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="15"/>
       <c r="B30" s="16"/>
       <c r="C30" s="16">
@@ -16943,20 +16943,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E789909-84FC-488D-8D94-3FAD76B00BC6}">
   <dimension ref="A1:B1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="22.83203125" style="2" customWidth="1"/>
-    <col min="3" max="26" width="7.6640625" style="2" customWidth="1"/>
-    <col min="27" max="16384" width="12.6640625" style="2"/>
+    <col min="1" max="1" width="20.28515625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="22.85546875" style="2" customWidth="1"/>
+    <col min="3" max="26" width="7.7109375" style="2" customWidth="1"/>
+    <col min="27" max="16384" width="12.7109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>18</v>
       </c>
@@ -16964,7 +16964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
         <v>-5</v>
       </c>
@@ -16972,7 +16972,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <v>-4</v>
       </c>
@@ -16980,7 +16980,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
         <v>-3</v>
       </c>
@@ -16988,7 +16988,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <v>-2</v>
       </c>
@@ -16996,7 +16996,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <v>-1</v>
       </c>
@@ -17004,7 +17004,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>0</v>
       </c>
@@ -17012,7 +17012,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <v>1</v>
       </c>
@@ -17020,7 +17020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <v>2</v>
       </c>
@@ -17028,7 +17028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <v>3</v>
       </c>
@@ -17036,7 +17036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <v>4</v>
       </c>
@@ -17044,7 +17044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
         <v>5</v>
       </c>
@@ -17052,7 +17052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
         <v>6</v>
       </c>
@@ -17060,996 +17060,996 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="14" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="22" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="23" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="24" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="25" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="26" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="27" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="28" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="29" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="30" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="31" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="32" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="21" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A18" r:id="rId1" xr:uid="{BB8AB8C5-9F96-41D8-B252-ACC21DAB1BB3}"/>
@@ -18062,20 +18062,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FC552F5-687A-B14F-ACE0-F13F8118F4F8}">
   <dimension ref="A1:Z30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="11" width="5" style="2" customWidth="1"/>
-    <col min="12" max="12" width="5.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="26" width="8.6640625" style="2" customWidth="1"/>
-    <col min="27" max="16384" width="14.1640625" style="2"/>
+    <col min="15" max="15" width="14.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="26" width="8.7109375" style="2" customWidth="1"/>
+    <col min="27" max="16384" width="14.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="68" t="s">
         <v>2</v>
       </c>
@@ -18105,7 +18105,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="70" t="s">
         <v>3</v>
       </c>
@@ -18135,7 +18135,7 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
-    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
       <c r="B3" s="1"/>
       <c r="C3" s="4"/>
@@ -18163,7 +18163,7 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A4" s="67" t="s">
         <v>4</v>
       </c>
@@ -18221,7 +18221,7 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A5" s="21"/>
       <c r="B5" s="6" t="s">
         <v>10</v>
@@ -18272,7 +18272,7 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
     </row>
-    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="23"/>
       <c r="B6" s="24" t="s">
         <v>24</v>
@@ -18320,7 +18320,7 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A7" s="11"/>
       <c r="B7" s="12" t="s">
         <v>23</v>
@@ -18350,7 +18350,7 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15"/>
       <c r="B8" s="16" t="s">
         <v>25</v>
@@ -18380,7 +18380,7 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
       <c r="B9" s="12"/>
       <c r="C9" s="12"/>
@@ -18408,7 +18408,7 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
     </row>
-    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15"/>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
@@ -18436,7 +18436,7 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A11" s="11"/>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
@@ -18464,7 +18464,7 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
@@ -18492,7 +18492,7 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A13" s="11"/>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
@@ -18520,7 +18520,7 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15"/>
       <c r="B14" s="16"/>
       <c r="C14" s="16"/>
@@ -18548,7 +18548,7 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A15" s="11"/>
       <c r="B15" s="12"/>
       <c r="C15" s="12"/>
@@ -18576,7 +18576,7 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15"/>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
@@ -18604,7 +18604,7 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A17" s="11"/>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
@@ -18632,7 +18632,7 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15"/>
       <c r="B18" s="16"/>
       <c r="C18" s="16"/>
@@ -18660,7 +18660,7 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A19" s="11"/>
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
@@ -18688,7 +18688,7 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15"/>
       <c r="B20" s="16"/>
       <c r="C20" s="16"/>
@@ -18716,7 +18716,7 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A21" s="11"/>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
@@ -18744,7 +18744,7 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15"/>
       <c r="B22" s="16"/>
       <c r="C22" s="16"/>
@@ -18772,7 +18772,7 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A23" s="11"/>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
@@ -18800,7 +18800,7 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15"/>
       <c r="B24" s="16"/>
       <c r="C24" s="16"/>
@@ -18828,7 +18828,7 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A25" s="11"/>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
@@ -18856,7 +18856,7 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15"/>
       <c r="B26" s="16"/>
       <c r="C26" s="16"/>
@@ -18884,7 +18884,7 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A27" s="11"/>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
@@ -18912,7 +18912,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="15"/>
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
@@ -18940,7 +18940,7 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -18968,7 +18968,7 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="15"/>
       <c r="B30" s="16"/>
       <c r="C30" s="16"/>
@@ -19012,20 +19012,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72BEDCE9-6DB6-684C-9A36-B24C0B788429}">
   <dimension ref="A1:Z30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="11" width="5" style="2" customWidth="1"/>
-    <col min="12" max="12" width="5.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="26" width="8.6640625" style="2" customWidth="1"/>
-    <col min="27" max="16384" width="14.1640625" style="2"/>
+    <col min="15" max="15" width="14.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="26" width="8.7109375" style="2" customWidth="1"/>
+    <col min="27" max="16384" width="14.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="68" t="s">
         <v>2</v>
       </c>
@@ -19055,7 +19055,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="70" t="s">
         <v>3</v>
       </c>
@@ -19085,7 +19085,7 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
-    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
       <c r="B3" s="1"/>
       <c r="C3" s="4"/>
@@ -19113,7 +19113,7 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A4" s="67" t="s">
         <v>4</v>
       </c>
@@ -19171,7 +19171,7 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A5" s="21"/>
       <c r="B5" s="6" t="s">
         <v>10</v>
@@ -19222,7 +19222,7 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
     </row>
-    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="23"/>
       <c r="B6" s="24" t="s">
         <v>24</v>
@@ -19270,7 +19270,7 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>14</v>
       </c>
@@ -19328,7 +19328,7 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15"/>
       <c r="B8" s="16" t="s">
         <v>25</v>
@@ -19391,7 +19391,7 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>15</v>
       </c>
@@ -19447,7 +19447,7 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
     </row>
-    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15"/>
       <c r="B10" s="16"/>
       <c r="C10" s="16">
@@ -19508,7 +19508,7 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>32</v>
       </c>
@@ -19564,7 +19564,7 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16">
@@ -19625,7 +19625,7 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>11</v>
       </c>
@@ -19681,7 +19681,7 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15"/>
       <c r="B14" s="16"/>
       <c r="C14" s="16">
@@ -19742,7 +19742,7 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>13</v>
       </c>
@@ -19798,7 +19798,7 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15"/>
       <c r="B16" s="16"/>
       <c r="C16" s="16">
@@ -19859,7 +19859,7 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>26</v>
       </c>
@@ -19915,7 +19915,7 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15"/>
       <c r="B18" s="16"/>
       <c r="C18" s="16">
@@ -19976,7 +19976,7 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>16</v>
       </c>
@@ -20002,7 +20002,7 @@
       <c r="I19" s="12">
         <v>4</v>
       </c>
-      <c r="J19" s="12">
+      <c r="J19" s="53">
         <v>3</v>
       </c>
       <c r="K19" s="12">
@@ -20032,7 +20032,7 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15"/>
       <c r="B20" s="16"/>
       <c r="C20" s="16">
@@ -20093,7 +20093,7 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>21</v>
       </c>
@@ -20149,7 +20149,7 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15"/>
       <c r="B22" s="16"/>
       <c r="C22" s="16">
@@ -20210,7 +20210,7 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>22</v>
       </c>
@@ -20266,7 +20266,7 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15"/>
       <c r="B24" s="16"/>
       <c r="C24" s="16">
@@ -20327,7 +20327,7 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>27</v>
       </c>
@@ -20383,7 +20383,7 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15"/>
       <c r="B26" s="16"/>
       <c r="C26" s="16">
@@ -20444,7 +20444,7 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>28</v>
       </c>
@@ -20500,7 +20500,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="15"/>
       <c r="B28" s="16"/>
       <c r="C28" s="16">
@@ -20561,7 +20561,7 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>12</v>
       </c>
@@ -20590,7 +20590,7 @@
       <c r="J29" s="12">
         <v>4</v>
       </c>
-      <c r="K29" s="12">
+      <c r="K29" s="53">
         <v>4</v>
       </c>
       <c r="L29" s="13">
@@ -20617,7 +20617,7 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="15"/>
       <c r="B30" s="16"/>
       <c r="C30" s="16">
@@ -20694,20 +20694,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{098E9CBB-8515-E247-BAE9-1E112AF74A33}">
   <dimension ref="A1:Z30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="11" width="5" style="2" customWidth="1"/>
-    <col min="12" max="12" width="5.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="26" width="8.6640625" style="2" customWidth="1"/>
-    <col min="27" max="16384" width="14.1640625" style="2"/>
+    <col min="15" max="15" width="14.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="26" width="8.7109375" style="2" customWidth="1"/>
+    <col min="27" max="16384" width="14.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="68" t="s">
         <v>2</v>
       </c>
@@ -20737,7 +20737,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="70" t="s">
         <v>3</v>
       </c>
@@ -20767,7 +20767,7 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
-    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
       <c r="B3" s="1"/>
       <c r="C3" s="4"/>
@@ -20795,7 +20795,7 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A4" s="67" t="s">
         <v>4</v>
       </c>
@@ -20853,7 +20853,7 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A5" s="21"/>
       <c r="B5" s="6" t="s">
         <v>10</v>
@@ -20904,7 +20904,7 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
     </row>
-    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="23"/>
       <c r="B6" s="24" t="s">
         <v>24</v>
@@ -20952,7 +20952,7 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A7" s="11"/>
       <c r="B7" s="12" t="s">
         <v>23</v>
@@ -20982,7 +20982,7 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15"/>
       <c r="B8" s="16" t="s">
         <v>25</v>
@@ -21012,7 +21012,7 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
       <c r="B9" s="12"/>
       <c r="C9" s="12"/>
@@ -21040,7 +21040,7 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
     </row>
-    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15"/>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
@@ -21068,7 +21068,7 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A11" s="11"/>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
@@ -21096,7 +21096,7 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
@@ -21124,7 +21124,7 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A13" s="11"/>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
@@ -21152,7 +21152,7 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15"/>
       <c r="B14" s="16"/>
       <c r="C14" s="16"/>
@@ -21180,7 +21180,7 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A15" s="11"/>
       <c r="B15" s="12"/>
       <c r="C15" s="12"/>
@@ -21208,7 +21208,7 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15"/>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
@@ -21236,7 +21236,7 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A17" s="11"/>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
@@ -21264,7 +21264,7 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15"/>
       <c r="B18" s="16"/>
       <c r="C18" s="16"/>
@@ -21292,7 +21292,7 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A19" s="11"/>
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
@@ -21320,7 +21320,7 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15"/>
       <c r="B20" s="16"/>
       <c r="C20" s="16"/>
@@ -21348,7 +21348,7 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A21" s="11"/>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
@@ -21376,7 +21376,7 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15"/>
       <c r="B22" s="16"/>
       <c r="C22" s="16"/>
@@ -21404,7 +21404,7 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A23" s="11"/>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
@@ -21432,7 +21432,7 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15"/>
       <c r="B24" s="16"/>
       <c r="C24" s="16"/>
@@ -21460,7 +21460,7 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A25" s="11"/>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
@@ -21488,7 +21488,7 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15"/>
       <c r="B26" s="16"/>
       <c r="C26" s="16"/>
@@ -21516,7 +21516,7 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A27" s="11"/>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
@@ -21544,7 +21544,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="15"/>
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
@@ -21572,7 +21572,7 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -21600,7 +21600,7 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="15"/>
       <c r="B30" s="16"/>
       <c r="C30" s="16"/>
@@ -21644,20 +21644,20 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4D1C59C-7F9E-CE4C-B410-088C8215B2AE}">
   <dimension ref="A1:Z10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="64" customWidth="1"/>
-    <col min="2" max="2" width="9.1640625" style="34" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" style="64" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" style="34" customWidth="1"/>
     <col min="3" max="11" width="5" style="34" customWidth="1"/>
-    <col min="12" max="12" width="5.1640625" style="34" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.1640625" style="34" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" style="34" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.140625" style="34" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5" style="34" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.5" style="34" customWidth="1"/>
-    <col min="16" max="26" width="8.6640625" style="34" customWidth="1"/>
-    <col min="27" max="16384" width="14.1640625" style="34"/>
+    <col min="15" max="15" width="9.42578125" style="34" customWidth="1"/>
+    <col min="16" max="26" width="8.7109375" style="34" customWidth="1"/>
+    <col min="27" max="16384" width="14.140625" style="34"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="17.25" x14ac:dyDescent="0.4">
       <c r="A1" s="71" t="s">
         <v>2</v>
       </c>
@@ -21687,7 +21687,7 @@
       <c r="Y1" s="35"/>
       <c r="Z1" s="35"/>
     </row>
-    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="73" t="s">
         <v>3</v>
       </c>
@@ -21717,7 +21717,7 @@
       <c r="Y2" s="35"/>
       <c r="Z2" s="35"/>
     </row>
-    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="60"/>
       <c r="B3" s="35"/>
       <c r="C3" s="37"/>
@@ -21745,7 +21745,7 @@
       <c r="Y3" s="35"/>
       <c r="Z3" s="35"/>
     </row>
-    <row r="4" spans="1:26" ht="40" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A4" s="61" t="s">
         <v>4</v>
       </c>
@@ -21803,7 +21803,7 @@
       <c r="Y4" s="36"/>
       <c r="Z4" s="36"/>
     </row>
-    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A5" s="62"/>
       <c r="B5" s="41" t="s">
         <v>10</v>
@@ -21854,7 +21854,7 @@
       <c r="Y5" s="36"/>
       <c r="Z5" s="36"/>
     </row>
-    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="63"/>
       <c r="B6" s="44" t="s">
         <v>24</v>
@@ -21902,7 +21902,7 @@
       <c r="Y6" s="36"/>
       <c r="Z6" s="36"/>
     </row>
-    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A7" s="65" t="s">
         <v>26</v>
       </c>
@@ -21960,7 +21960,7 @@
       <c r="Y7" s="35"/>
       <c r="Z7" s="35"/>
     </row>
-    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="66"/>
       <c r="B8" s="50" t="s">
         <v>25</v>
@@ -22023,7 +22023,7 @@
       <c r="Y8" s="35"/>
       <c r="Z8" s="35"/>
     </row>
-    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A9" s="65" t="s">
         <v>29</v>
       </c>
@@ -22079,7 +22079,7 @@
       <c r="Y9" s="35"/>
       <c r="Z9" s="35"/>
     </row>
-    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="66"/>
       <c r="B10" s="50"/>
       <c r="C10" s="16">
@@ -22156,20 +22156,20 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D570C757-B716-FC4E-9C7E-AF3ECCA3BD91}">
   <dimension ref="A1:Z20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="11" width="5" style="2" customWidth="1"/>
-    <col min="12" max="12" width="5.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="26" width="8.6640625" style="2" customWidth="1"/>
-    <col min="27" max="16384" width="14.1640625" style="2"/>
+    <col min="15" max="15" width="14.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="26" width="8.7109375" style="2" customWidth="1"/>
+    <col min="27" max="16384" width="14.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="68" t="s">
         <v>2</v>
       </c>
@@ -22199,7 +22199,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="70" t="s">
         <v>3</v>
       </c>
@@ -22229,7 +22229,7 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
-    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
       <c r="B3" s="1"/>
       <c r="C3" s="4"/>
@@ -22257,7 +22257,7 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A4" s="67" t="s">
         <v>4</v>
       </c>
@@ -22315,7 +22315,7 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A5" s="21"/>
       <c r="B5" s="6" t="s">
         <v>10</v>
@@ -22366,7 +22366,7 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
     </row>
-    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="23"/>
       <c r="B6" s="24" t="s">
         <v>24</v>
@@ -22414,7 +22414,7 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>26</v>
       </c>
@@ -22472,7 +22472,7 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15"/>
       <c r="B8" s="16" t="s">
         <v>25</v>
@@ -22535,7 +22535,7 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>13</v>
       </c>
@@ -22591,7 +22591,7 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
     </row>
-    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15"/>
       <c r="B10" s="16"/>
       <c r="C10" s="16">
@@ -22652,7 +22652,7 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>30</v>
       </c>
@@ -22705,7 +22705,7 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
@@ -22739,7 +22739,7 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -22795,7 +22795,7 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15"/>
       <c r="B14" s="16"/>
       <c r="C14" s="16">
@@ -22856,7 +22856,7 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>12</v>
       </c>
@@ -22885,7 +22885,7 @@
       <c r="J15" s="12">
         <v>6</v>
       </c>
-      <c r="K15" s="12">
+      <c r="K15" s="53">
         <v>4</v>
       </c>
       <c r="L15" s="13">
@@ -22912,7 +22912,7 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15"/>
       <c r="B16" s="16"/>
       <c r="C16" s="16">
@@ -22973,7 +22973,7 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>27</v>
       </c>
@@ -23026,7 +23026,7 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15"/>
       <c r="B18" s="16"/>
       <c r="C18" s="16">
@@ -23087,7 +23087,7 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>14</v>
       </c>
@@ -23143,7 +23143,7 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15"/>
       <c r="B20" s="16"/>
       <c r="C20" s="16">
@@ -23220,20 +23220,20 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EB761E0-E44A-664C-81AB-F821FA9D3978}">
   <dimension ref="A1:Z28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="11" width="5" style="2" customWidth="1"/>
-    <col min="12" max="12" width="5.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="26" width="8.6640625" style="2" customWidth="1"/>
-    <col min="27" max="16384" width="14.1640625" style="2"/>
+    <col min="15" max="15" width="14.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="26" width="8.7109375" style="2" customWidth="1"/>
+    <col min="27" max="16384" width="14.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="68" t="s">
         <v>2</v>
       </c>
@@ -23263,7 +23263,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="70" t="s">
         <v>3</v>
       </c>
@@ -23293,7 +23293,7 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
-    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
       <c r="B3" s="1"/>
       <c r="C3" s="4"/>
@@ -23321,7 +23321,7 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A4" s="67" t="s">
         <v>4</v>
       </c>
@@ -23379,7 +23379,7 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A5" s="21"/>
       <c r="B5" s="6" t="s">
         <v>10</v>
@@ -23430,7 +23430,7 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
     </row>
-    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="23"/>
       <c r="B6" s="24" t="s">
         <v>24</v>
@@ -23478,7 +23478,7 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>14</v>
       </c>
@@ -23536,7 +23536,7 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15"/>
       <c r="B8" s="16" t="s">
         <v>25</v>
@@ -23599,7 +23599,7 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>15</v>
       </c>
@@ -23655,7 +23655,7 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
     </row>
-    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15"/>
       <c r="B10" s="16"/>
       <c r="C10" s="16">
@@ -23716,7 +23716,7 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
@@ -23769,7 +23769,7 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16">
@@ -23830,7 +23830,7 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>26</v>
       </c>
@@ -23886,7 +23886,7 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15"/>
       <c r="B14" s="16"/>
       <c r="C14" s="16">
@@ -23947,7 +23947,7 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>28</v>
       </c>
@@ -24000,7 +24000,7 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15"/>
       <c r="B16" s="16"/>
       <c r="C16" s="16">
@@ -24061,7 +24061,7 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>27</v>
       </c>
@@ -24114,7 +24114,7 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15"/>
       <c r="B18" s="16"/>
       <c r="C18" s="16">
@@ -24175,7 +24175,7 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>12</v>
       </c>
@@ -24204,7 +24204,7 @@
       <c r="J19" s="12">
         <v>5</v>
       </c>
-      <c r="K19" s="12">
+      <c r="K19" s="53">
         <v>4</v>
       </c>
       <c r="L19" s="13">
@@ -24231,7 +24231,7 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15"/>
       <c r="B20" s="16"/>
       <c r="C20" s="16">
@@ -24292,7 +24292,7 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>11</v>
       </c>
@@ -24321,7 +24321,7 @@
       <c r="J21" s="12">
         <v>4</v>
       </c>
-      <c r="K21" s="12">
+      <c r="K21" s="53">
         <v>4</v>
       </c>
       <c r="L21" s="13">
@@ -24348,7 +24348,7 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15"/>
       <c r="B22" s="16"/>
       <c r="C22" s="16">
@@ -24409,7 +24409,7 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>13</v>
       </c>
@@ -24465,7 +24465,7 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15"/>
       <c r="B24" s="16"/>
       <c r="C24" s="16">
@@ -24526,7 +24526,7 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>31</v>
       </c>
@@ -24582,7 +24582,7 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15"/>
       <c r="B26" s="16"/>
       <c r="C26" s="16">
@@ -24643,7 +24643,7 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>32</v>
       </c>
@@ -24699,7 +24699,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="15"/>
       <c r="B28" s="16"/>
       <c r="C28" s="16">
@@ -24776,20 +24776,20 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDDF5DB3-65C4-44BD-9129-FA096F865907}">
   <dimension ref="A1:Z34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" style="2" customWidth="1"/>
     <col min="3" max="11" width="5" style="2" customWidth="1"/>
-    <col min="12" max="12" width="5.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17" style="2" customWidth="1"/>
-    <col min="16" max="26" width="8.6640625" style="2" customWidth="1"/>
-    <col min="27" max="16384" width="14.1640625" style="2"/>
+    <col min="16" max="26" width="8.7109375" style="2" customWidth="1"/>
+    <col min="27" max="16384" width="14.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="68" t="s">
         <v>2</v>
       </c>
@@ -24819,7 +24819,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="70" t="s">
         <v>3</v>
       </c>
@@ -24849,7 +24849,7 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
-    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
       <c r="B3" s="1"/>
       <c r="C3" s="4"/>
@@ -24877,7 +24877,7 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A4" s="67" t="s">
         <v>4</v>
       </c>
@@ -24935,7 +24935,7 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
       <c r="B5" s="6" t="s">
         <v>10</v>
@@ -24986,7 +24986,7 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
     </row>
-    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="23"/>
       <c r="B6" s="24" t="s">
         <v>24</v>
@@ -25034,7 +25034,7 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>14</v>
       </c>
@@ -25065,7 +25065,7 @@
       <c r="J7" s="12">
         <v>7</v>
       </c>
-      <c r="K7" s="12">
+      <c r="K7" s="53">
         <v>4</v>
       </c>
       <c r="L7" s="13">
@@ -25092,7 +25092,7 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15"/>
       <c r="B8" s="16" t="s">
         <v>25</v>
@@ -25155,7 +25155,7 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>33</v>
       </c>
@@ -25211,7 +25211,7 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
     </row>
-    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15"/>
       <c r="B10" s="16"/>
       <c r="C10" s="16">
@@ -25272,7 +25272,7 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>28</v>
       </c>
@@ -25328,7 +25328,7 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16">
@@ -25389,7 +25389,7 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>11</v>
       </c>
@@ -25445,7 +25445,7 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15"/>
       <c r="B14" s="16"/>
       <c r="C14" s="16">
@@ -25506,7 +25506,7 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>29</v>
       </c>
@@ -25562,7 +25562,7 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15"/>
       <c r="B16" s="16"/>
       <c r="C16" s="16">
@@ -25623,7 +25623,7 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>34</v>
       </c>
@@ -25649,7 +25649,7 @@
       <c r="I17" s="12">
         <v>3</v>
       </c>
-      <c r="J17" s="12">
+      <c r="J17" s="53">
         <v>3</v>
       </c>
       <c r="K17" s="12">
@@ -25679,7 +25679,7 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15"/>
       <c r="B18" s="16"/>
       <c r="C18" s="16">
@@ -25740,7 +25740,7 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>32</v>
       </c>
@@ -25796,7 +25796,7 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15"/>
       <c r="B20" s="16"/>
       <c r="C20" s="16">
@@ -25857,7 +25857,7 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>27</v>
       </c>
@@ -25913,7 +25913,7 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15"/>
       <c r="B22" s="16"/>
       <c r="C22" s="16">
@@ -25974,7 +25974,7 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>36</v>
       </c>
@@ -25994,7 +25994,7 @@
       <c r="G23" s="12">
         <v>6</v>
       </c>
-      <c r="H23" s="12">
+      <c r="H23" s="53">
         <v>3</v>
       </c>
       <c r="I23" s="12">
@@ -26030,7 +26030,7 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15"/>
       <c r="B24" s="16"/>
       <c r="C24" s="16">
@@ -26091,7 +26091,7 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>35</v>
       </c>
@@ -26147,7 +26147,7 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15"/>
       <c r="B26" s="16"/>
       <c r="C26" s="16">
@@ -26208,7 +26208,7 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>12</v>
       </c>
@@ -26264,7 +26264,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="15"/>
       <c r="B28" s="16"/>
       <c r="C28" s="16">
@@ -26325,7 +26325,7 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>31</v>
       </c>
@@ -26381,7 +26381,7 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="15"/>
       <c r="B30" s="16"/>
       <c r="C30" s="16">
@@ -26442,7 +26442,7 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>26</v>
       </c>
@@ -26498,7 +26498,7 @@
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
     </row>
-    <row r="32" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="15"/>
       <c r="B32" s="16"/>
       <c r="C32" s="16">
@@ -26559,7 +26559,7 @@
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
     </row>
-    <row r="33" spans="1:26" ht="19" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
         <v>16</v>
       </c>
@@ -26615,7 +26615,7 @@
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
     </row>
-    <row r="34" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="15"/>
       <c r="B34" s="16"/>
       <c r="C34" s="16">
